--- a/Aii竞彩推荐_2026-05-10.xlsx
+++ b/Aii竞彩推荐_2026-05-10.xlsx
@@ -614,7 +614,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 10:03</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:47</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP1.56/3.45/5.03 让球-1</t>
+          <t>SP1.53/3.55/5.15 让球-1</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP3.08/3.40/1.96 让球+1</t>
+          <t>SP3.12/3.35/1.96 让球+1</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.93/3.40/3.15 让球-1</t>
+          <t>SP1.97/3.35/3.10 让球-1</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP4.60/3.55/1.59 让球+1</t>
+          <t>SP4.30/3.40/1.66 让球+1</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP2.97/3.80/1.89 让球+1</t>
+          <t>SP3.02/3.72/1.89 让球+1</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>SP2.55/3.12/2.40 让球+1</t>
+          <t>SP2.65/3.15/2.30 让球+1</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>SP2.49/3.32/2.35 让球+1</t>
+          <t>SP2.57/3.32/2.28 让球+1</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>SP1.63/3.45/4.42 让球-1</t>
+          <t>SP1.60/3.50/4.58 让球-1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>SP2.65/3.65/2.09 让球+1</t>
+          <t>SP2.74/3.65/2.04 让球+1</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>SP6.05/4.00/1.40 让球+1</t>
+          <t>SP6.25/4.10/1.38 让球+1</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 10:03）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 11:47）</t>
         </is>
       </c>
     </row>
@@ -2172,13 +2172,13 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5.03</v>
+        <v>5.15</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.13</t>
         </is>
       </c>
     </row>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="F46" s="7" t="n">
         <v>1.96</v>
@@ -2264,13 +2264,13 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -2279,17 +2279,17 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
           <t>3.85</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
@@ -2310,13 +2310,13 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -2325,17 +2325,17 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>1.89</v>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -2601,17 +2601,17 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.20</t>
         </is>
       </c>
     </row>
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>3.32</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -2647,17 +2647,17 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.85</t>
         </is>
       </c>
     </row>
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>4.42</v>
+        <v>4.58</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -2831,17 +2831,17 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -2954,13 +2954,13 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="E62" s="7" t="n">
         <v>3.65</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2969,17 +2969,17 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -3092,13 +3092,13 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -3107,17 +3107,17 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.37</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=207%P平=94%P客=64%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=213%P平=92%P客=63%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=110%P平=100%P客=173%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=107%P平=100%P客=171%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=176%P平=100%P客=108%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=170%P平=100%P客=108%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -3778,19 +3778,19 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>平负</t>
-        </is>
-      </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
           <t>2元</t>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=75%P平=97%P客=217%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=79%P平=100%P客=205%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=121%P平=95%P客=191%|泊松比分0-1|半全场平负|大小球小2.5(43%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=119%P平=96%P客=190%|泊松比分0-1|半全场平负|大小球小2.5(43%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -4063,54 +4063,54 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>周日010</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>水晶宫vs埃弗顿</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>2/10</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J89" s="10" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=122%P平=100%P客=130%|泊松比分1-1|半全场胜胜|大小球小2.5(52%)|让球+1=输盘/让平/让负|放弃</t>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=119%P平=100%P客=137%|泊松比分1-2|半全场胜胜|大小球大2.5(64%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>贝叶斯P主=133%P平=100%P客=141%|泊松比分2-2|半全场胜胜|大小球大2.5(67%)|让球+1=输盘/让平/让负|放弃</t>
+          <t>贝叶斯P主=129%P平=100%P客=146%|泊松比分2-2|半全场胜胜|大小球大2.5(67%)|让球+1=输盘/让平/让负|放弃</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=210%P平=99%P客=77%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=214%P平=98%P客=75%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -4506,17 +4506,17 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=135%P平=98%P客=171%|泊松比分1-2|半全场平胜|大小球大2.5(58%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=130%P平=98%P客=175%|泊松比分1-2|半全场平负|大小球大2.5(58%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=55%P平=84%P客=239%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=54%P平=82%P客=244%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>3.08/3.40/1.96</t>
+          <t>3.12/3.35/1.96</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>周日003</t>
+          <t>周日004</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>柏太阳神</t>
+          <t>千叶市原</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>川崎前锋</t>
+          <t>町田泽维</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>1.93/3.40/3.15</t>
+          <t>4.30/3.40/1.66</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜/平局</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>让+1盘</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>2.97/3.80/1.89</t>
+          <t>3.02/3.72/1.89</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>1.63/3.45/4.42</t>
+          <t>1.60/3.50/4.58</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>1.56/3.45/5.03</t>
+          <t>1.53/3.55/5.15</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
@@ -5769,27 +5769,27 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>周日004</t>
+          <t>周日005</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>日职</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>千叶市原</t>
+          <t>维罗纳</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>町田泽维</t>
+          <t>科莫</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>4.60/3.55/1.59</t>
+          <t>8.25/4.65/1.26</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5819,27 +5819,27 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>周日005</t>
+          <t>周日009</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>英超</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>维罗纳</t>
+          <t>伯恩利</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>科莫</t>
+          <t>维拉</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>8.25/4.65/1.26</t>
+          <t>4.95/3.90/1.49</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>周日009</t>
+          <t>周日012</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>伯恩利</t>
+          <t>克雷莫纳</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>维拉</t>
+          <t>比萨</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>4.95/3.90/1.49</t>
+          <t>1.56/3.55/4.85</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>客胜/平局</t>
+          <t>主胜/平局</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>让-1盘</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5923,7 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日024 吉达联合vs达马克 → 主胜/平局 (信心9/10)</t>
+          <t>⬜ 周日024 吉达联合vs达马克 → 主胜/平局 (信心7/10)</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日003 柏太阳神vs川崎前锋 → 主胜/平局 (信心6/10)</t>
+          <t>⬜ 周日004 千叶市原vs町田泽维 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
@@ -6064,14 +6064,14 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003</t>
+          <t>周日024+周日002+周日004</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)
 ·大阪钢巴:客胜(1.96)
-·柏太阳神:主胜(1.93)</t>
+·千叶市原:客胜(1.66)</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>1.30×1.96×1.93=4.92</t>
+          <t>1.30×1.96×1.66=4.23</t>
         </is>
       </c>
     </row>
@@ -6101,14 +6101,14 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006</t>
+          <t>周日024+周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)
 ·大阪钢巴:客胜(1.96)
-·柏太阳神:主胜(1.93)
+·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)</t>
         </is>
       </c>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>1.30×1.96×1.93×1.89=9.29</t>
+          <t>1.30×1.96×1.66×1.89=7.99</t>
         </is>
       </c>
     </row>
@@ -6139,14 +6139,14 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006+周日013</t>
+          <t>周日024+周日002+周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)
 ·大阪钢巴:客胜(1.96)
-·柏太阳神:主胜(1.93)
+·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)</t>
         </is>
@@ -6161,12 +6161,12 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>1.30×1.96×1.93×1.89×1.89=17.57</t>
+          <t>1.30×1.96×1.66×1.89×1.89=15.11</t>
         </is>
       </c>
     </row>
@@ -6178,17 +6178,17 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006+周日013+周日015</t>
+          <t>周日024+周日002+周日004+周日006+周日013+周日015</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)
 ·大阪钢巴:客胜(1.96)
-·柏太阳神:主胜(1.93)
+·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)
-·毕尔巴鄂:主胜(1.63)</t>
+·毕尔巴鄂:主胜(1.60)</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>1.30×1.96×1.93×1.89×1.89×1.63=28.63</t>
+          <t>1.30×1.96×1.66×1.89×1.89×1.60=24.17</t>
         </is>
       </c>
     </row>
@@ -6385,9 +6385,9 @@
         <is>
           <t xml:space="preserve">时间：13:00
 联赛：韩职
-竞彩SP：1.56 / 3.45 / 5.03
-让球SP(真实)：2.98/3.15/2.10
-差值分析：P主=207% P平=94% P客=64%
+竞彩SP：1.53 / 3.55 / 5.15
+让球SP(真实)：2.92/3.15/2.13
+差值分析：P主=213% P平=92% P客=63%
 推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6405,10 +6405,10 @@
         <is>
           <t xml:space="preserve">时间：14:00
 联赛：日职
-竞彩SP：3.08 / 3.40 / 1.96
+竞彩SP：3.12 / 3.35 / 1.96
 让球SP(真实)：1.65/3.70/3.95
-差值分析：P主=110% P平=100% P客=173%
-推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:平胜
+差值分析：P主=107% P平=100% P客=171%
+推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:负负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6425,10 +6425,10 @@
         <is>
           <t xml:space="preserve">时间：15:00
 联赛：日职
-竞彩SP：1.93 / 3.40 / 3.15
-让球SP(真实)：3.85/3.75/1.66
-差值分析：P主=176% P平=100% P客=108%
-推荐：主胜 信心6/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+竞彩SP：1.97 / 3.35 / 3.10
+让球SP(真实)：3.98/3.85/1.62
+差值分析：P主=170% P平=100% P客=108%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6445,10 +6445,10 @@
         <is>
           <t xml:space="preserve">时间：16:00
 联赛：日职
-竞彩SP：4.60 / 3.55 / 1.59
-让球SP(真实)：2.05/3.35/2.92
-差值分析：P主=75% P平=97% P客=217%
-推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
+竞彩SP：4.30 / 3.40 / 1.66
+让球SP(真实)：1.96/3.21/3.25
+差值分析：P主=79% P平=100% P客=205%
+推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:负负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6485,9 +6485,9 @@
         <is>
           <t xml:space="preserve">时间：19:30
 联赛：德乙
-竞彩SP：2.97 / 3.80 / 1.89
+竞彩SP：3.02 / 3.72 / 1.89
 让球SP(真实)：1.70/4.00/3.43
-差值分析：P主=121% P平=95% P客=191%
+差值分析：P主=119% P平=96% P客=190%
 推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(43%) 备选半全场:负负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6508,7 +6508,7 @@
 竞彩SP：2.15 / 3.40 / 2.70
 让球SP(真实)：4.45/4.00/1.53
 差值分析：P主=158% P平=100% P客=126%
-推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6565,10 +6565,10 @@
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：2.55 / 3.12 / 2.40
-让球SP(真实)：1.43/4.15/5.30
-差值分析：P主=122% P平=100% P客=130%
-推荐：不投 信心2/10 比分1-1(泊松) 半全场胜胜 大小球小2.5(52%) 备选半全场:平胜
+竞彩SP：2.65 / 3.15 / 2.30
+让球SP(真实)：1.45/4.05/5.20
+差值分析：P主=119% P平=100% P客=137%
+推荐：客胜 信心2/10 比分1-2(泊松) 半全场胜胜 大小球大2.5(64%) 备选半全场:平胜
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6585,9 +6585,9 @@
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：2.49 / 3.32 / 2.35
-让球SP(真实)：1.44/4.25/5.00
-差值分析：P主=133% P平=100% P客=141%
+竞彩SP：2.57 / 3.32 / 2.28
+让球SP(真实)：1.46/4.20/4.85
+差值分析：P主=129% P平=100% P客=146%
 推荐：不投 信心2/10 比分2-2(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6665,9 +6665,9 @@
         <is>
           <t xml:space="preserve">时间：22:15
 联赛：西甲
-竞彩SP：1.63 / 3.45 / 4.42
-让球SP(真实)：3.08/3.35/1.98
-差值分析：P主=210% P平=99% P客=77%
+竞彩SP：1.60 / 3.50 / 4.58
+让球SP(真实)：3.04/3.25/2.03
+差值分析：P主=214% P平=98% P客=75%
 推荐：主胜 信心6/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6725,10 +6725,10 @@
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
-竞彩SP：2.65 / 3.65 / 2.09
-让球SP(真实)：1.56/4.15/4.05
-差值分析：P主=135% P平=98% P客=171%
-推荐：客胜 信心4/10 比分1-2(泊松) 半全场平胜 大小球大2.5(58%) 备选半全场:平负
+竞彩SP：2.74 / 3.65 / 2.04
+让球SP(真实)：1.58/4.05/4.00
+差值分析：P主=130% P平=98% P客=175%
+推荐：客胜 信心2/10 比分1-2(泊松) 半全场平负 大小球大2.5(58%) 备选半全场:平胜
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6785,9 +6785,9 @@
         <is>
           <t xml:space="preserve">时间：00:00
 联赛：意甲
-竞彩SP：6.05 / 4.00 / 1.40
-让球SP(真实)：2.44/3.30/2.40
-差值分析：P主=55% P平=84% P客=239%
+竞彩SP：6.25 / 4.10 / 1.38
+让球SP(真实)：2.50/3.25/2.37
+差值分析：P主=54% P平=82% P客=244%
 推荐：客胜 信心5/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:胜负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6808,7 +6808,7 @@
 竞彩SP：2.79 / 2.70 / 2.50
 让球SP(真实)：1.39/3.80/6.80
 差值分析：P主=76% P平=79% P客=85%
-推荐：平局 信心4/10 比分1-1(泊松) 半全场平胜 大小球小2.5(43%) 备选半全场:胜胜
+推荐：平局 信心2/10 比分1-1(泊松) 半全场平胜 大小球小2.5(43%) 备选半全场:胜胜
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6848,7 +6848,7 @@
 竞彩SP：1.30 / 4.60 / 7.00
 让球SP(真实)：2.03/3.43/2.90
 差值分析：P主=343% P平=97% P客=64%
-推荐：主胜 信心9/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(47%) 备选半全场:平胜
+推荐：主胜 信心7/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(47%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6908,7 +6908,7 @@
 竞彩SP：2.22 / 3.20 / 2.73
 让球SP(真实)：4.95/3.85/1.50
 差值分析：P主=144% P平=100% P客=117%
-推荐：主胜 信心4/10 比分1-0(泊松) 半全场平胜 大小球小2.5(42%) 备选半全场:胜胜
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场平胜 大小球小2.5(42%) 备选半全场:胜胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6948,7 +6948,7 @@
 竞彩SP：2.14 / 3.60 / 2.60
 让球SP(真实)：4.45/4.00/1.53
 差值分析：P主=166% P平=99% P客=137%
-推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:负胜
+推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:负胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6968,7 +6968,7 @@
 竞彩SP：2.23 / 3.40 / 2.59
 让球SP(真实)：4.80/4.00/1.49
 差值分析：P主=152% P平=100% P客=131%
-推荐：主胜 信心4/10 比分1-0(泊松) 半全场平胜 大小球小2.5(43%) 备选半全场:胜胜
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场平胜 大小球小2.5(43%) 备选半全场:胜胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -7133,14 +7133,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003</t>
+          <t>周日024+周日002+周日004</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)
 ·大阪钢巴:客胜(1.96)
-·柏太阳神:主胜(1.93)</t>
+·千叶市原:客胜(1.66)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -7173,14 +7173,14 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006</t>
+          <t>周日024+周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)
 ·大阪钢巴:客胜(1.96)
-·柏太阳神:主胜(1.93)
+·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)</t>
         </is>
       </c>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006+周日013</t>
+          <t>周日024+周日002+周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)
 ·大阪钢巴:客胜(1.96)
-·柏太阳神:主胜(1.93)
+·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)</t>
         </is>
@@ -7256,17 +7256,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006+周日013+周日015</t>
+          <t>周日024+周日002+周日004+周日006+周日013+周日015</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)
 ·大阪钢巴:客胜(1.96)
-·柏太阳神:主胜(1.93)
+·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)
-·毕尔巴鄂:主胜(1.63)</t>
+·毕尔巴鄂:主胜(1.60)</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -7352,14 +7352,14 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003</t>
+          <t>周日024+周日002+周日004</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:2-0(6.5)
 ·大阪钢巴:0-1(9.8)
-·柏太阳神:1-0(9.7)</t>
+·千叶市原:0-1(8.3)</t>
         </is>
       </c>
       <c r="E11" s="21" t="n">
@@ -7408,14 +7408,14 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003</t>
+          <t>周日024+周日002+周日004</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)/让平/让负
 ·大阪钢巴:客胜(1.96)/让平/让负
-·柏太阳神:主胜(1.93)/让平/让负</t>
+·千叶市原:客胜(1.66)/让平/让负</t>
         </is>
       </c>
       <c r="E13" s="21" t="n">
@@ -7450,14 +7450,14 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006</t>
+          <t>周日024+周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:主胜(1.30)/让平/让负
 ·大阪钢巴:客胜(1.96)/让平/让负
-·柏太阳神:主胜(1.93)/让平/让负
+·千叶市原:客胜(1.66)/让平/让负
 ·杜塞多夫:客胜(1.89)/让平/让负</t>
         </is>
       </c>
@@ -7548,14 +7548,14 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003</t>
+          <t>周日024+周日002+周日004</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:胜胜(2.2)
 ·大阪钢巴:平负(3.5)
-·柏太阳神:胜胜(2.2)</t>
+·千叶市原:平负(3.5)</t>
         </is>
       </c>
       <c r="E17" s="21" t="n">
@@ -7590,14 +7590,14 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006</t>
+          <t>周日024+周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:胜胜(2.2)
 ·大阪钢巴:平负(3.5)
-·柏太阳神:胜胜(2.2)
+·千叶市原:平负(3.5)
 ·杜塞多夫:平负(3.5)</t>
         </is>
       </c>
@@ -7633,14 +7633,14 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006+周日013</t>
+          <t>周日024+周日002+周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:胜胜(2.2)
 ·大阪钢巴:平负(3.5)
-·柏太阳神:胜胜(2.2)
+·千叶市原:平负(3.5)
 ·杜塞多夫:平负(3.5)
 ·佛罗伦萨:胜胜(2.2)</t>
         </is>
@@ -7677,14 +7677,14 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日003+周日006+周日013+周日015</t>
+          <t>周日024+周日002+周日004+周日006+周日013+周日015</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
           <t>·吉达联合:胜胜(2.2)
 ·大阪钢巴:平负(3.5)
-·柏太阳神:胜胜(2.2)
+·千叶市原:平负(3.5)
 ·杜塞多夫:平负(3.5)
 ·佛罗伦萨:胜胜(2.2)
 ·毕尔巴鄂:胜胜(2.2)</t>

--- a/Aii竞彩推荐_2026-05-10.xlsx
+++ b/Aii竞彩推荐_2026-05-10.xlsx
@@ -614,7 +614,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:47</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:54</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 11:47）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 11:54）</t>
         </is>
       </c>
     </row>
@@ -5219,37 +5219,37 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>周日024</t>
+          <t>周日002</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>日职</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>吉达联合</t>
+          <t>大阪钢巴</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>达马克</t>
+          <t>广岛三箭</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>1.30/4.60/7.00</t>
+          <t>3.12/3.35/1.96</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜/平局</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>让+1盘</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>周日002</t>
+          <t>周日004</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -5279,17 +5279,17 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>大阪钢巴</t>
+          <t>千叶市原</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>广岛三箭</t>
+          <t>町田泽维</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>3.12/3.35/1.96</t>
+          <t>4.30/3.40/1.66</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5314,350 +5314,350 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="6" t="n">
+      <c r="A117" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>周日004</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>日职</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>千叶市原</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>町田泽维</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>4.30/3.40/1.66</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>周日006</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>德乙</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>杜塞多夫</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>埃沃斯堡</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>3.02/3.72/1.89</t>
+        </is>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
         <is>
           <t>6/10</t>
         </is>
       </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J117" s="6" t="inlineStr">
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J117" s="12" t="inlineStr">
         <is>
           <t>让+1盘</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="n">
+      <c r="A118" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>周日006</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>德乙</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>杜塞多夫</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>埃沃斯堡</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>3.02/3.72/1.89</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>周日013</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>佛罗伦萨</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>热那亚</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>1.89/3.15/3.55</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
         <is>
           <t>6/10</t>
         </is>
       </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J118" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="n">
+      <c r="A119" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>周日013</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>周日015</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>毕尔巴鄂</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>巴伦西亚</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>1.60/3.50/4.58</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>周日016</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>荷甲</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>费耶诺德</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>阿尔克马</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>1.65/3.95/3.70</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>周日020</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>科隆</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>海登海姆</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>1.90/3.75/2.98</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>周日025</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
         <is>
           <t>意甲</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>佛罗伦萨</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>热那亚</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>1.89/3.15/3.55</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H119" s="6" t="inlineStr">
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>AC米兰</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>亚特兰大</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>1.90/3.28/3.35</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
         <is>
           <t>6/10</t>
         </is>
       </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J119" s="6" t="inlineStr">
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>周日015</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>周日026</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
         <is>
           <t>西甲</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>毕尔巴鄂</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>巴伦西亚</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>1.60/3.50/4.58</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>巴萨</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>皇马</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>1.51/4.65/3.96</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
         <is>
           <t>6/10</t>
         </is>
       </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J120" s="6" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>周日016</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>费耶诺德</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>阿尔克马</t>
-        </is>
-      </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>1.65/3.95/3.70</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H121" s="6" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J121" s="6" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>周日020</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>德甲</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>科隆</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>海登海姆</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>1.90/3.75/2.98</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J122" s="6" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>周日025</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>AC米兰</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>亚特兰大</t>
-        </is>
-      </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>1.90/3.28/3.35</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J123" s="6" t="inlineStr">
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5669,27 +5669,27 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>周日026</t>
+          <t>周日001</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>韩职</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>巴萨</t>
+          <t>蔚山现代</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>皇马</t>
+          <t>富川FC</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>1.51/4.65/3.96</t>
+          <t>1.53/3.55/5.15</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
@@ -5714,200 +5714,200 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="n">
+      <c r="A125" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>周日001</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>韩职</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>蔚山现代</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>富川FC</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>1.53/3.55/5.15</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>周日005</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>维罗纳</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>科莫</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>8.25/4.65/1.26</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
         <is>
           <t>5/10</t>
         </is>
       </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J125" s="6" t="inlineStr">
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>让+1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>周日009</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>伯恩利</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>维拉</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>4.95/3.90/1.49</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J126" s="12" t="inlineStr">
+        <is>
+          <t>让+1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>周日012</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>克雷莫纳</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>比萨</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>1.56/3.55/4.85</t>
+        </is>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J127" s="12" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>周日005</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>维罗纳</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>科莫</t>
-        </is>
-      </c>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>8.25/4.65/1.26</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>周日017</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>荷甲</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>阿贾克斯</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>乌德勒支</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>1.49/4.25/4.50</t>
+        </is>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
         <is>
           <t>5/10</t>
         </is>
       </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>周日009</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>伯恩利</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>维拉</t>
-        </is>
-      </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>4.95/3.90/1.49</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J127" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>周日012</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>克雷莫纳</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>比萨</t>
-        </is>
-      </c>
-      <c r="F128" s="6" t="inlineStr">
-        <is>
-          <t>1.56/3.55/4.85</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I128" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J128" s="6" t="inlineStr">
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J128" s="12" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5916,70 +5916,70 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>📋 任选9方案（全双选防冷）</t>
+          <t>📋 任选9方案（7胆+2双=4注=8元）</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日024 吉达联合vs达马克 → 主胜/平局 (信心7/10)</t>
+          <t>⬜ 周日002 大阪钢巴vs广岛三箭 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日002 大阪钢巴vs广岛三箭 → 客胜/平局 (信心6/10)</t>
+          <t>⬜ 周日004 千叶市原vs町田泽维 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日004 千叶市原vs町田泽维 → 客胜/平局 (信心6/10)</t>
+          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜/平局 (信心6/10)</t>
+          <t>⬜ 周日013 佛罗伦萨vs热那亚 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日013 佛罗伦萨vs热那亚 → 主胜/平局 (信心6/10)</t>
+          <t>⬜ 周日015 毕尔巴鄂vs巴伦西亚 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日015 毕尔巴鄂vs巴伦西亚 → 主胜/平局 (信心6/10)</t>
+          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜/平局 (信心6/10)</t>
+          <t>⬜ 周日020 科隆vs海登海姆 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日020 科隆vs海登海姆 → 主胜/平局 (信心6/10)</t>
+          <t>⬜ 周日025 AC米兰vs亚特兰大 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日025 AC米兰vs亚特兰大 → 主胜/平局 (信心6/10)</t>
+          <t>⬜ 周日026 巴萨vs皇马 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
@@ -6028,13 +6028,13 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002</t>
+          <t>周日002+周日004</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)</t>
+          <t>·大阪钢巴:客胜(1.96)
+·千叶市原:客胜(1.66)</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>1.30×1.96=2.55</t>
+          <t>1.96×1.66=3.25</t>
         </is>
       </c>
     </row>
@@ -6064,14 +6064,14 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004</t>
+          <t>周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)</t>
+          <t>·大阪钢巴:客胜(1.96)
+·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>1.30×1.96×1.66=4.23</t>
+          <t>1.96×1.66×1.89=6.15</t>
         </is>
       </c>
     </row>
@@ -6101,96 +6101,96 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004+周日006</t>
+          <t>周日002+周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>7.99</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>1.30×1.96×1.66×1.89=7.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>周日024+周日002+周日004+周日006+周日013</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)
+          <t>·大阪钢巴:客胜(1.96)
 ·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)</t>
         </is>
       </c>
-      <c r="D153" s="6" t="n">
+      <c r="D152" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E152" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="G153" s="6" t="inlineStr">
-        <is>
-          <t>1.30×1.96×1.66×1.89×1.89=15.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>周日024+周日002+周日004+周日006+周日013+周日015</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>11.62</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>1.96×1.66×1.89×1.89=11.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>周日002+周日004+周日006+周日013+周日015</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>·大阪钢巴:客胜(1.96)
 ·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)
 ·毕尔巴鄂:主胜(1.60)</t>
         </is>
       </c>
+      <c r="D153" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>18.60</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>1.96×1.66×1.89×1.89×1.60=18.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>周日002+周日004+周日006+周日013+周日015+周日016</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>·大阪钢巴:客胜(1.96)
+·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)
+·佛罗伦萨:主胜(1.89)
+·毕尔巴鄂:主胜(1.60)
+·费耶诺德:主胜(1.65)</t>
+        </is>
+      </c>
       <c r="D154" s="6" t="n">
         <v>1</v>
       </c>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>24.17</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>1.30×1.96×1.66×1.89×1.89×1.60=24.17</t>
+          <t>1.96×1.66×1.89×1.89×1.60×1.65=30.68</t>
         </is>
       </c>
     </row>
@@ -7094,13 +7094,13 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002</t>
+          <t>周日002+周日004</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)</t>
+          <t>·大阪钢巴:客胜(1.96)
+·千叶市原:客胜(1.66)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004</t>
+          <t>周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)</t>
+          <t>·大阪钢巴:客胜(1.96)
+·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -7173,102 +7173,102 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004+周日006</t>
+          <t>周日002+周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>6.56元</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>+228%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>周日024+周日002+周日004+周日006+周日013</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)
+          <t>·大阪钢巴:客胜(1.96)
 ·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="21" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="E6" s="21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>12.02元</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>+501%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>周日024+周日002+周日004+周日006+周日013+周日015</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>·吉达联合:主胜(1.30)
-·大阪钢巴:客胜(1.96)
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>6.56元</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>+228%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>周日002+周日004+周日006+周日013+周日015</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>·大阪钢巴:客胜(1.96)
 ·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)
 ·毕尔巴鄂:主胜(1.60)</t>
         </is>
       </c>
+      <c r="D7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>12.02元</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>+501%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>周日002+周日004+周日006+周日013+周日015+周日016</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>·大阪钢巴:客胜(1.96)
+·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)
+·佛罗伦萨:主胜(1.89)
+·毕尔巴鄂:主胜(1.60)
+·费耶诺德:主胜(1.65)</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n">
         <v>1</v>
       </c>
@@ -7311,13 +7311,13 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002</t>
+          <t>周日002+周日004</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:2-0(6.5)
-·大阪钢巴:0-1(9.8)</t>
+          <t>·大阪钢巴:0-1(9.8)
+·千叶市原:0-1(8.3)</t>
         </is>
       </c>
       <c r="E10" s="21" t="n">
@@ -7352,14 +7352,14 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004</t>
+          <t>周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:2-0(6.5)
-·大阪钢巴:0-1(9.8)
-·千叶市原:0-1(8.3)</t>
+          <t>·大阪钢巴:0-1(9.8)
+·千叶市原:0-1(8.3)
+·杜塞多夫:0-1(9.4)</t>
         </is>
       </c>
       <c r="E11" s="21" t="n">
@@ -7408,14 +7408,14 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004</t>
+          <t>周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:主胜(1.30)/让平/让负
-·大阪钢巴:客胜(1.96)/让平/让负
-·千叶市原:客胜(1.66)/让平/让负</t>
+          <t>·大阪钢巴:客胜(1.96)/让平/让负
+·千叶市原:客胜(1.66)/让平/让负
+·杜塞多夫:客胜(1.89)/让平/让负</t>
         </is>
       </c>
       <c r="E13" s="21" t="n">
@@ -7450,15 +7450,15 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004+周日006</t>
+          <t>周日002+周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:主胜(1.30)/让平/让负
-·大阪钢巴:客胜(1.96)/让平/让负
+          <t>·大阪钢巴:客胜(1.96)/让平/让负
 ·千叶市原:客胜(1.66)/让平/让负
-·杜塞多夫:客胜(1.89)/让平/让负</t>
+·杜塞多夫:客胜(1.89)/让平/让负
+·佛罗伦萨:主胜(1.89)/让平/让负</t>
         </is>
       </c>
       <c r="E14" s="21" t="n">
@@ -7507,13 +7507,13 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002</t>
+          <t>周日002+周日004</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:胜胜(2.2)
-·大阪钢巴:平负(3.5)</t>
+          <t>·大阪钢巴:平负(3.5)
+·千叶市原:平负(3.5)</t>
         </is>
       </c>
       <c r="E16" s="21" t="n">
@@ -7548,14 +7548,14 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004</t>
+          <t>周日002+周日004+周日006</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:胜胜(2.2)
-·大阪钢巴:平负(3.5)
-·千叶市原:平负(3.5)</t>
+          <t>·大阪钢巴:平负(3.5)
+·千叶市原:平负(3.5)
+·杜塞多夫:平负(3.5)</t>
         </is>
       </c>
       <c r="E17" s="21" t="n">
@@ -7590,104 +7590,104 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>周日024+周日002+周日004+周日006</t>
+          <t>周日002+周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>·吉达联合:胜胜(2.2)
-·大阪钢巴:平负(3.5)
-·千叶市原:平负(3.5)
-·杜塞多夫:平负(3.5)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>30.25</v>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>60.50元</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>+2925%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>周日024+周日002+周日004+周日006+周日013</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>·吉达联合:胜胜(2.2)
-·大阪钢巴:平负(3.5)
+          <t>·大阪钢巴:平负(3.5)
 ·千叶市原:平负(3.5)
 ·杜塞多夫:平负(3.5)
 ·佛罗伦萨:胜胜(2.2)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="E18" s="21" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>133.10元</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>+6555%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>60.50元</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>+2925%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>半全场</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>周日024+周日002+周日004+周日006+周日013+周日015</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>·吉达联合:胜胜(2.2)
-·大阪钢巴:平负(3.5)
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>周日002+周日004+周日006+周日013+周日015</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>·大阪钢巴:平负(3.5)
 ·千叶市原:平负(3.5)
 ·杜塞多夫:平负(3.5)
 ·佛罗伦萨:胜胜(2.2)
 ·毕尔巴鄂:胜胜(2.2)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>133.10元</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>+6555%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>半全场</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>周日002+周日004+周日006+周日013+周日015+周日016</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>·大阪钢巴:平负(3.5)
+·千叶市原:平负(3.5)
+·杜塞多夫:平负(3.5)
+·佛罗伦萨:胜胜(2.2)
+·毕尔巴鄂:胜胜(2.2)
+·费耶诺德:胜胜(2.2)</t>
         </is>
       </c>
       <c r="E20" s="21" t="n">

--- a/Aii竞彩推荐_2026-05-10.xlsx
+++ b/Aii竞彩推荐_2026-05-10.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,9 +60,6 @@
       <color rgb="001A3C6E"/>
       <sz val="11"/>
     </font>
-    <font>
-      <sz val="9"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -97,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -163,17 +160,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,9 +212,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -614,7 +602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:54</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 12:23</t>
         </is>
       </c>
     </row>
@@ -729,7 +717,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP1.53/3.55/5.15 让球-1</t>
+          <t>SP1.49/3.62/5.50 让球-1</t>
         </is>
       </c>
     </row>
@@ -776,7 +764,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP3.12/3.35/1.96 让球+1</t>
+          <t>SP3.12/3.30/1.98 让球+1</t>
         </is>
       </c>
     </row>
@@ -823,7 +811,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.97/3.35/3.10 让球-1</t>
+          <t>SP2.04/3.30/2.98 让球-1</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1093,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP4.95/3.90/1.49 让球+1</t>
+          <t>SP5.10/3.95/1.47 让球+1</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 11:54）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 12:23）</t>
         </is>
       </c>
     </row>
@@ -2172,13 +2160,13 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
@@ -2187,17 +2175,17 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.22</t>
         </is>
       </c>
     </row>
@@ -2221,10 +2209,10 @@
         <v>3.12</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -2233,7 +2221,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -2243,7 +2231,7 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.15</t>
         </is>
       </c>
     </row>
@@ -2264,13 +2252,13 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -2279,17 +2267,17 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
     </row>
@@ -2540,13 +2528,13 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -2555,7 +2543,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -2565,7 +2553,7 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3630,7 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=213%P平=92%P客=63%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=220%P平=90%P客=60%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3652,7 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3674,7 +3662,7 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -3684,7 +3672,7 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -3694,7 +3682,7 @@
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=107%P平=100%P客=171%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=106%P平=100%P客=167%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3714,7 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -3746,7 +3734,7 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=170%P平=100%P客=108%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=162%P平=100%P客=111%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3870,7 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
@@ -3934,7 +3922,7 @@
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4058,7 +4046,7 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=75%P平=96%P客=251%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=73%P平=95%P客=255%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4494,7 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -4662,7 +4650,7 @@
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -4719,12 +4707,12 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>平平</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="I101" s="8" t="inlineStr">
@@ -4766,7 +4754,7 @@
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -4870,7 +4858,7 @@
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -5078,7 +5066,7 @@
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -5130,7 +5118,7 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
@@ -5219,7 +5207,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>周日002</t>
+          <t>周日004</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -5229,17 +5217,17 @@
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>大阪钢巴</t>
+          <t>千叶市原</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>广岛三箭</t>
+          <t>町田泽维</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>3.12/3.35/1.96</t>
+          <t>4.30/3.40/1.66</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
@@ -5264,50 +5252,50 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="n">
+      <c r="A116" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>周日004</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>日职</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>千叶市原</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>町田泽维</t>
-        </is>
-      </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>4.30/3.40/1.66</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>周日006</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>德乙</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>杜塞多夫</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>埃沃斯堡</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>3.02/3.72/1.89</t>
+        </is>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr">
         <is>
           <t>6/10</t>
         </is>
       </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J116" s="6" t="inlineStr">
+      <c r="I116" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J116" s="12" t="inlineStr">
         <is>
           <t>让+1盘</t>
         </is>
@@ -5319,32 +5307,32 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>周日006</t>
+          <t>周日013</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>德乙</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>杜塞多夫</t>
+          <t>佛罗伦萨</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>埃沃斯堡</t>
+          <t>热那亚</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>3.02/3.72/1.89</t>
+          <t>1.89/3.15/3.55</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
@@ -5359,7 +5347,7 @@
       </c>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>让-1盘</t>
         </is>
       </c>
     </row>
@@ -5369,27 +5357,27 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>周日013</t>
+          <t>周日015</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>佛罗伦萨</t>
+          <t>毕尔巴鄂</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>热那亚</t>
+          <t>巴伦西亚</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>1.89/3.15/3.55</t>
+          <t>1.60/3.50/4.58</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
@@ -5419,27 +5407,27 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>周日015</t>
+          <t>周日016</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>荷甲</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>毕尔巴鄂</t>
+          <t>费耶诺德</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>巴伦西亚</t>
+          <t>阿尔克马</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>1.60/3.50/4.58</t>
+          <t>1.65/3.95/3.70</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -5469,27 +5457,27 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>周日016</t>
+          <t>周日020</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>荷甲</t>
+          <t>德甲</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>费耶诺德</t>
+          <t>科隆</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>阿尔克马</t>
+          <t>海登海姆</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>1.65/3.95/3.70</t>
+          <t>1.90/3.75/2.98</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -5519,27 +5507,27 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>周日020</t>
+          <t>周日025</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>科隆</t>
+          <t>AC米兰</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>海登海姆</t>
+          <t>亚特兰大</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>1.90/3.75/2.98</t>
+          <t>1.90/3.28/3.35</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -5569,147 +5557,147 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>周日025</t>
+          <t>周日026</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>巴萨</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>皇马</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>1.51/4.65/3.96</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>周日001</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>蔚山现代</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>富川FC</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>1.49/3.62/5.50</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>周日005</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
           <t>意甲</t>
         </is>
       </c>
-      <c r="D122" s="12" t="inlineStr">
-        <is>
-          <t>AC米兰</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>亚特兰大</t>
-        </is>
-      </c>
-      <c r="F122" s="12" t="inlineStr">
-        <is>
-          <t>1.90/3.28/3.35</t>
-        </is>
-      </c>
-      <c r="G122" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I122" s="12" t="inlineStr">
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>维罗纳</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>科莫</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>8.25/4.65/1.26</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J122" s="12" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B123" s="12" t="inlineStr">
-        <is>
-          <t>周日026</t>
-        </is>
-      </c>
-      <c r="C123" s="12" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D123" s="12" t="inlineStr">
-        <is>
-          <t>巴萨</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>皇马</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>1.51/4.65/3.96</t>
-        </is>
-      </c>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H123" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I123" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J123" s="12" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>周日001</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>韩职</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>蔚山现代</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>富川FC</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>1.53/3.55/5.15</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J124" s="6" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>让+1盘</t>
         </is>
       </c>
     </row>
@@ -5719,27 +5707,27 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>周日005</t>
+          <t>周日009</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>英超</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>维罗纳</t>
+          <t>伯恩利</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>科莫</t>
+          <t>维拉</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>8.25/4.65/1.26</t>
+          <t>5.10/3.95/1.47</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -5769,32 +5757,32 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>周日009</t>
+          <t>周日012</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>伯恩利</t>
+          <t>克雷莫纳</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>维拉</t>
+          <t>比萨</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>4.95/3.90/1.49</t>
+          <t>1.56/3.55/4.85</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -5809,7 +5797,7 @@
       </c>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>让-1盘</t>
         </is>
       </c>
     </row>
@@ -5819,27 +5807,27 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>周日012</t>
+          <t>周日017</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>荷甲</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>克雷莫纳</t>
+          <t>阿贾克斯</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>比萨</t>
+          <t>乌德勒支</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>1.56/3.55/4.85</t>
+          <t>1.49/4.25/4.50</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -5869,32 +5857,32 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>周日017</t>
+          <t>周日019</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>荷甲</t>
+          <t>英超</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>阿贾克斯</t>
+          <t>西汉姆联</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>乌德勒支</t>
+          <t>阿森纳</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>1.49/4.25/4.50</t>
+          <t>5.40/4.10/1.43</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -5909,7 +5897,7 @@
       </c>
       <c r="J128" s="12" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>让+1盘</t>
         </is>
       </c>
     </row>
@@ -5923,63 +5911,63 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日002 大阪钢巴vs广岛三箭 → 客胜/平局 (信心6/10)</t>
+          <t>⬜ 周日004 千叶市原vs町田泽维 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日004 千叶市原vs町田泽维 → 客胜/平局 (信心6/10)</t>
+          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜 (信心6/10)</t>
+          <t>⬜ 周日013 佛罗伦萨vs热那亚 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日013 佛罗伦萨vs热那亚 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日015 毕尔巴鄂vs巴伦西亚 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日015 毕尔巴鄂vs巴伦西亚 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日020 科隆vs海登海姆 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日020 科隆vs海登海姆 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日025 AC米兰vs亚特兰大 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日025 AC米兰vs亚特兰大 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日026 巴萨vs皇马 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日026 巴萨vs皇马 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日001 蔚山现代vs富川FC → 主胜/平局 (信心5/10)</t>
         </is>
       </c>
     </row>
@@ -6028,13 +6016,13 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004</t>
+          <t>周日004+周日006</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)</t>
+          <t>·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
@@ -6047,12 +6035,12 @@
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>1.96×1.66=3.25</t>
+          <t>1.66×1.89=3.14</t>
         </is>
       </c>
     </row>
@@ -6064,14 +6052,14 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006</t>
+          <t>周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)</t>
+          <t>·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)
+·佛罗伦萨:主胜(1.89)</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -6084,12 +6072,12 @@
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>1.96×1.66×1.89=6.15</t>
+          <t>1.66×1.89×1.89=5.93</t>
         </is>
       </c>
     </row>
@@ -6101,96 +6089,96 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006+周日013</t>
+          <t>周日004+周日006+周日013+周日015</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>11.62</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>1.96×1.66×1.89×1.89=11.62</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日004+周日006+周日013+周日015</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
+          <t>·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)
 ·毕尔巴鄂:主胜(1.60)</t>
         </is>
       </c>
-      <c r="D153" s="6" t="n">
+      <c r="D152" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E152" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>18.60</t>
-        </is>
-      </c>
-      <c r="G153" s="6" t="inlineStr">
-        <is>
-          <t>1.96×1.66×1.89×1.89×1.60=18.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日004+周日006+周日013+周日015+周日016</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>9.49</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>1.66×1.89×1.89×1.60=9.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>周日004+周日006+周日013+周日015+周日016</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)
 ·毕尔巴鄂:主胜(1.60)
 ·费耶诺德:主胜(1.65)</t>
         </is>
       </c>
+      <c r="D153" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>15.65</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>1.66×1.89×1.89×1.60×1.65=15.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>周日004+周日006+周日013+周日015+周日016+周日020</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)
+·佛罗伦萨:主胜(1.89)
+·毕尔巴鄂:主胜(1.60)
+·费耶诺德:主胜(1.65)
+·科隆:主胜(1.90)</t>
+        </is>
+      </c>
       <c r="D154" s="6" t="n">
         <v>1</v>
       </c>
@@ -6201,12 +6189,12 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>1.96×1.66×1.89×1.89×1.60×1.65=30.68</t>
+          <t>1.66×1.89×1.89×1.60×1.65×1.90=29.74</t>
         </is>
       </c>
     </row>
@@ -6385,9 +6373,9 @@
         <is>
           <t xml:space="preserve">时间：13:00
 联赛：韩职
-竞彩SP：1.53 / 3.55 / 5.15
-让球SP(真实)：2.92/3.15/2.13
-差值分析：P主=213% P平=92% P客=63%
+竞彩SP：1.49 / 3.62 / 5.50
+让球SP(真实)：2.79/3.12/2.22
+差值分析：P主=220% P平=90% P客=60%
 推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6405,10 +6393,10 @@
         <is>
           <t xml:space="preserve">时间：14:00
 联赛：日职
-竞彩SP：3.12 / 3.35 / 1.96
-让球SP(真实)：1.65/3.70/3.95
-差值分析：P主=107% P平=100% P客=171%
-推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:负负
+竞彩SP：3.12 / 3.30 / 1.98
+让球SP(真实)：1.62/3.70/4.15
+差值分析：P主=106% P平=100% P客=167%
+推荐：客胜 信心2/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:平胜
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6425,9 +6413,9 @@
         <is>
           <t xml:space="preserve">时间：15:00
 联赛：日职
-竞彩SP：1.97 / 3.35 / 3.10
-让球SP(真实)：3.98/3.85/1.62
-差值分析：P主=170% P平=100% P客=108%
+竞彩SP：2.04 / 3.30 / 2.98
+让球SP(真实)：4.05/3.95/1.59
+差值分析：P主=162% P平=100% P客=111%
 推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6545,9 +6533,9 @@
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：4.95 / 3.90 / 1.49
-让球SP(真实)：2.27/3.40/2.53
-差值分析：P主=75% P平=96% P客=251%
+竞彩SP：5.10 / 3.95 / 1.47
+让球SP(真实)：2.32/3.40/2.48
+差值分析：P主=73% P平=95% P客=255%
 推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -7094,34 +7082,31 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004</t>
+          <t>周日004+周日006</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)</t>
+          <t>·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="inlineStr">
-        <is>
-          <t>2.92元</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>+46%</t>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>6.28元</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>3.14倍</t>
         </is>
       </c>
     </row>
@@ -7133,35 +7118,32 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006</t>
+          <t>周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)</t>
+          <t>·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)
+·佛罗伦萨:主胜(1.89)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G5" s="21" t="inlineStr">
-        <is>
-          <t>3.86元</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>+93%</t>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>11.86元</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>5.93倍</t>
         </is>
       </c>
     </row>
@@ -7173,121 +7155,112 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006+周日013</t>
+          <t>周日004+周日006+周日013+周日015</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>6.56元</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>+228%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日004+周日006+周日013+周日015</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
+          <t>·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)
 ·毕尔巴鄂:主胜(1.60)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="21" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>12.02元</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>+501%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日004+周日006+周日013+周日015+周日016</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.96)
-·千叶市原:客胜(1.66)
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>18.98元</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>9.49倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>周日004+周日006+周日013+周日015+周日016</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>·千叶市原:客胜(1.66)
 ·杜塞多夫:客胜(1.89)
 ·佛罗伦萨:主胜(1.89)
 ·毕尔巴鄂:主胜(1.60)
 ·费耶诺德:主胜(1.65)</t>
         </is>
       </c>
+      <c r="D7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>31.30元</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>15.65倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>周日004+周日006+周日013+周日015+周日016+周日020</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>·千叶市原:客胜(1.66)
+·杜塞多夫:客胜(1.89)
+·佛罗伦萨:主胜(1.89)
+·毕尔巴鄂:主胜(1.60)
+·费耶诺德:主胜(1.65)
+·科隆:主胜(1.90)</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>22.00元</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>+1000%</t>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>59.48元</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>29.74倍</t>
         </is>
       </c>
     </row>
@@ -7311,31 +7284,31 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004</t>
+          <t>周日004+周日006</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:0-1(9.8)
-·千叶市原:0-1(8.3)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
+          <t>·千叶市原:0-1(8.3)
+·杜塞多夫:0-1(9.4)</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>74.40元</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>+3620%</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>约157元</t>
         </is>
       </c>
     </row>
@@ -7352,32 +7325,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006</t>
+          <t>周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:0-1(9.8)
-·千叶市原:0-1(8.3)
-·杜塞多夫:0-1(9.4)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>245.5</v>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
+          <t>·千叶市原:0-1(8.3)
+·杜塞多夫:0-1(9.4)
+·佛罗伦萨:2-1(9.4)</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>491.00元</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>+24450%</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>约1482元</t>
         </is>
       </c>
     </row>
@@ -7408,32 +7381,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006</t>
+          <t>周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.96)/让平/让负
-·千叶市原:客胜(1.66)/让平/让负
-·杜塞多夫:客胜(1.89)/让平/让负</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+          <t>·千叶市原:客胜(1.66)/让平/让负
+·杜塞多夫:客胜(1.89)/让平/让负
+·佛罗伦萨:主胜(1.89)/让平/让负</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>3.86元</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>+93%</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>11.86元</t>
         </is>
       </c>
     </row>
@@ -7450,33 +7423,33 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006+周日013</t>
+          <t>周日004+周日006+周日013+周日015</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.96)/让平/让负
-·千叶市原:客胜(1.66)/让平/让负
+          <t>·千叶市原:客胜(1.66)/让平/让负
 ·杜塞多夫:客胜(1.89)/让平/让负
-·佛罗伦萨:主胜(1.89)/让平/让负</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
+·佛罗伦萨:主胜(1.89)/让平/让负
+·毕尔巴鄂:主胜(1.60)/让平/让负</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>9.49</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>6.56元</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>+228%</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>18.97元</t>
         </is>
       </c>
     </row>
@@ -7507,31 +7480,31 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004</t>
+          <t>周日004+周日006</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:平负(3.5)
-·千叶市原:平负(3.5)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
+          <t>·千叶市原:平负(3.5)
+·杜塞多夫:平负(3.5)</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>12.25</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>9.68元</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>+384%</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>24.50元</t>
         </is>
       </c>
     </row>
@@ -7548,32 +7521,32 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006</t>
+          <t>周日004+周日006+周日013</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:平负(3.5)
-·千叶市原:平负(3.5)
-·杜塞多夫:平负(3.5)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
+          <t>·千叶市原:平负(3.5)
+·杜塞多夫:平负(3.5)
+·佛罗伦萨:胜胜(2.2)</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>26.95</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>24.20元</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>+1110%</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>53.90元</t>
         </is>
       </c>
     </row>
@@ -7590,122 +7563,122 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日004+周日006+周日013</t>
+          <t>周日004+周日006+周日013+周日015</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:平负(3.5)
-·千叶市原:平负(3.5)
-·杜塞多夫:平负(3.5)
-·佛罗伦萨:胜胜(2.2)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>30.25</v>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>60.50元</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>+2925%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日004+周日006+周日013+周日015</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:平负(3.5)
-·千叶市原:平负(3.5)
+          <t>·千叶市原:平负(3.5)
 ·杜塞多夫:平负(3.5)
 ·佛罗伦萨:胜胜(2.2)
 ·毕尔巴鄂:胜胜(2.2)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="E18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>59.29</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>133.10元</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>+6555%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>118.58元</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>半全场</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日004+周日006+周日013+周日015+周日016</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:平负(3.5)
-·千叶市原:平负(3.5)
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>周日004+周日006+周日013+周日015+周日016</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>·千叶市原:平负(3.5)
 ·杜塞多夫:平负(3.5)
 ·佛罗伦萨:胜胜(2.2)
 ·毕尔巴鄂:胜胜(2.2)
 ·费耶诺德:胜胜(2.2)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="n">
-        <v>146.41</v>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="E19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>130.44</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>292.82元</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>+14541%</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>260.88元</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>半全场</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>周日004+周日006+周日013+周日015+周日016+周日020</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>·千叶市原:平负(3.5)
+·杜塞多夫:平负(3.5)
+·佛罗伦萨:胜胜(2.2)
+·毕尔巴鄂:胜胜(2.2)
+·费耶诺德:胜胜(2.2)
+·科隆:胜胜(2.2)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>286.96</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>573.93元</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-10.xlsx
+++ b/Aii竞彩推荐_2026-05-10.xlsx
@@ -595,21 +595,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🌍 2026-05-10 周六30场竞彩推荐+14场任9</t>
+          <t>🌍 2026-05-10 周日30场竞彩推荐+14场胜负彩(查lottery.gov.cn期号)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 12:23</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 15:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>⏱ 停售：21:00(周六001-021)/次日(周六022-030)</t>
+          <t>⏱ 停售：21:00(周日001-021)/次日(周日022-030)</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2025-26赛季末段，保级+欧战争夺激烈。30场竞彩+14场有奖期。</t>
+          <t>2025-26赛季末段，保级+欧战争夺激烈。30场竞彩+14场(需查lottery.gov.cn官方奖期)。</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP1.49/3.62/5.50 让球-1</t>
+          <t>SP1.51/3.55/5.40 让球-1</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP3.12/3.30/1.98 让球+1</t>
+          <t>SP3.45/3.14/1.92 让球+1</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP2.04/3.30/2.98 让球-1</t>
+          <t>SP1.90/3.35/3.28 让球-1</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP4.30/3.40/1.66 让球+1</t>
+          <t>SP4.00/3.25/1.75 让球+1</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.15/3.40/2.70 让球-1</t>
+          <t>SP2.20/3.40/2.63 让球-1</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP5.10/3.95/1.47 让球+1</t>
+          <t>SP5.30/4.00/1.45 让球+1</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>SP2.65/3.15/2.30 让球+1</t>
+          <t>SP2.73/3.05/2.30 让球+1</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>SP1.56/3.55/4.85 让球-1</t>
+          <t>SP1.58/3.50/4.75 让球-1</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>SP1.89/3.15/3.55 让球-1</t>
+          <t>SP1.89/3.08/3.63 让球-1</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>SP1.65/3.95/3.70 让球-1</t>
+          <t>SP1.68/3.90/3.60 让球-1</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>SP5.40/4.10/1.43 让球+1</t>
+          <t>SP5.50/4.20/1.41 让球+1</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>SP6.25/4.10/1.38 让球+1</t>
+          <t>SP6.42/4.10/1.37 让球+1</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>SP1.30/4.60/7.00 让球-1</t>
+          <t>SP1.32/4.50/6.70 让球-1</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>SP2.22/3.20/2.73 让球-1</t>
+          <t>SP2.23/3.15/2.75 让球-1</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>SP2.14/3.60/2.60 让球-1</t>
+          <t>SP2.19/3.55/2.56 让球-1</t>
         </is>
       </c>
     </row>
@@ -2080,14 +2080,14 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>SP2.23/3.40/2.59 让球-1</t>
+          <t>SP2.25/3.35/2.59 让球-1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 12:23）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 15:57）</t>
         </is>
       </c>
     </row>
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -2221,17 +2221,17 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -2267,17 +2267,17 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -2298,13 +2298,13 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -2313,17 +2313,17 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
@@ -2359,17 +2359,17 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
     </row>
@@ -2436,13 +2436,13 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>3.4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -2451,17 +2451,17 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
     </row>
@@ -2528,13 +2528,13 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.44</t>
         </is>
       </c>
     </row>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="F54" s="7" t="n">
         <v>2.3</v>
@@ -2589,17 +2589,17 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.10</t>
         </is>
       </c>
     </row>
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -2715,10 +2715,10 @@
         <v>1.89</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2865,17 +2865,17 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -3003,17 +3003,17 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>6.25</v>
+        <v>6.42</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>4.1</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.33</t>
         </is>
       </c>
     </row>
@@ -3218,13 +3218,13 @@
         </is>
       </c>
       <c r="D68" s="7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
@@ -3371,17 +3371,17 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
     </row>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="F74" s="7" t="n">
         <v>2.59</v>
@@ -3509,17 +3509,17 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=220%P平=90%P客=60%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=216%P平=92%P客=60%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3667,14 +3667,14 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
           <t>2元</t>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=106%P平=100%P客=167%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=91%P平=100%P客=164%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=162%P平=100%P客=111%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=176%P平=100%P客=102%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3771,14 +3771,14 @@
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>负负</t>
-        </is>
-      </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
           <t>2元</t>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=79%P平=100%P客=205%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=81%P平=100%P客=186%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
           <t>平负</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>负负</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=158%P平=100%P客=126%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=155%P平=100%P客=129%|泊松比分1-0|半全场平胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3979,12 +3979,12 @@
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=73%P平=95%P客=255%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=71%P平=94%P客=259%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=119%P平=100%P客=137%|泊松比分1-2|半全场胜胜|大小球大2.5(64%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=112%P平=100%P客=133%|泊松比分1-2|半全场胜胜|大小球大2.5(64%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>负胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=209%P平=92%P客=67%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=206%P平=93%P客=68%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=167%P平=100%P客=89%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=163%P平=100%P客=85%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4291,12 +4291,12 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=220%P平=92%P客=98%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=216%P平=93%P客=101%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
           <t>平负</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=70%P平=92%P客=264%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=69%P平=90%P客=269%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=54%P平=82%P客=244%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=52%P平=82%P客=246%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平平</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I101" s="8" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="J103" s="13" t="inlineStr">
         <is>
-          <t>贝叶斯P主=343%P平=97%P客=64%|泊松比分2-0|半全场胜胜|大小球小2.5(47%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=337%P平=99%P客=66%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4967,14 +4967,14 @@
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
           <t>2元</t>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=144%P平=100%P客=117%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=141%P平=100%P客=115%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=166%P平=99%P客=137%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=162%P平=100%P客=138%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5123,14 +5123,14 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
           <t>2元</t>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=152%P平=100%P客=131%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=149%P平=100%P客=129%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5207,147 +5207,147 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
+          <t>周日002</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>日职</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>大阪钢巴</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>广岛三箭</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>3.45/3.14/1.92</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>让+1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>周日003</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>日职</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>柏太阳神</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>川崎前锋</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>1.90/3.35/3.28</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
           <t>周日004</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>日职</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>千叶市原</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>町田泽维</t>
         </is>
       </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>4.30/3.40/1.66</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>4.00/3.25/1.75</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
         <is>
           <t>客胜/平局</t>
         </is>
       </c>
-      <c r="H115" s="6" t="inlineStr">
+      <c r="H117" s="6" t="inlineStr">
         <is>
           <t>6/10</t>
         </is>
       </c>
-      <c r="I115" s="6" t="inlineStr">
+      <c r="I117" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J115" s="6" t="inlineStr">
+      <c r="J117" s="6" t="inlineStr">
         <is>
           <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t>周日006</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>德乙</t>
-        </is>
-      </c>
-      <c r="D116" s="12" t="inlineStr">
-        <is>
-          <t>杜塞多夫</t>
-        </is>
-      </c>
-      <c r="E116" s="12" t="inlineStr">
-        <is>
-          <t>埃沃斯堡</t>
-        </is>
-      </c>
-      <c r="F116" s="12" t="inlineStr">
-        <is>
-          <t>3.02/3.72/1.89</t>
-        </is>
-      </c>
-      <c r="G116" s="12" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H116" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I116" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J116" s="12" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B117" s="12" t="inlineStr">
-        <is>
-          <t>周日013</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D117" s="12" t="inlineStr">
-        <is>
-          <t>佛罗伦萨</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>热那亚</t>
-        </is>
-      </c>
-      <c r="F117" s="12" t="inlineStr">
-        <is>
-          <t>1.89/3.15/3.55</t>
-        </is>
-      </c>
-      <c r="G117" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I117" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J117" s="12" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
         </is>
       </c>
     </row>
@@ -5357,32 +5357,32 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>周日015</t>
+          <t>周日006</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>德乙</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>毕尔巴鄂</t>
+          <t>杜塞多夫</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>巴伦西亚</t>
+          <t>埃沃斯堡</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>1.60/3.50/4.58</t>
+          <t>3.02/3.72/1.89</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="J118" s="12" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>让+1盘</t>
         </is>
       </c>
     </row>
@@ -5407,27 +5407,27 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>周日016</t>
+          <t>周日012</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>荷甲</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>费耶诺德</t>
+          <t>克雷莫纳</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>阿尔克马</t>
+          <t>比萨</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>1.65/3.95/3.70</t>
+          <t>1.58/3.50/4.75</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -5457,27 +5457,27 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>周日020</t>
+          <t>周日013</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>科隆</t>
+          <t>佛罗伦萨</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>海登海姆</t>
+          <t>热那亚</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>1.90/3.75/2.98</t>
+          <t>1.89/3.08/3.63</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -5507,27 +5507,27 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>周日025</t>
+          <t>周日015</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>AC米兰</t>
+          <t>毕尔巴鄂</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>亚特兰大</t>
+          <t>巴伦西亚</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>1.90/3.28/3.35</t>
+          <t>1.60/3.50/4.58</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -5557,27 +5557,27 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>周日026</t>
+          <t>周日016</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>荷甲</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>巴萨</t>
+          <t>费耶诺德</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>皇马</t>
+          <t>阿尔克马</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>1.51/4.65/3.96</t>
+          <t>1.68/3.90/3.60</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -5602,50 +5602,50 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="n">
+      <c r="A123" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>周日001</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>韩职</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>蔚山现代</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>富川FC</t>
-        </is>
-      </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>1.49/3.62/5.50</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J123" s="6" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>周日020</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>科隆</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>海登海姆</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>1.90/3.75/2.98</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>周日005</t>
+          <t>周日025</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
@@ -5667,27 +5667,27 @@
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>维罗纳</t>
+          <t>AC米兰</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>科莫</t>
+          <t>亚特兰大</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>8.25/4.65/1.26</t>
+          <t>1.90/3.28/3.35</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I124" s="12" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="J124" s="12" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>让-1盘</t>
         </is>
       </c>
     </row>
@@ -5707,95 +5707,95 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>周日009</t>
+          <t>周日026</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>伯恩利</t>
+          <t>巴萨</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>维拉</t>
+          <t>皇马</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>5.10/3.95/1.47</t>
+          <t>1.51/4.65/3.96</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>周日001</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>蔚山现代</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>富川FC</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>1.51/3.55/5.40</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
           <t>5/10</t>
         </is>
       </c>
-      <c r="I125" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J125" s="12" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B126" s="12" t="inlineStr">
-        <is>
-          <t>周日012</t>
-        </is>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D126" s="12" t="inlineStr">
-        <is>
-          <t>克雷莫纳</t>
-        </is>
-      </c>
-      <c r="E126" s="12" t="inlineStr">
-        <is>
-          <t>比萨</t>
-        </is>
-      </c>
-      <c r="F126" s="12" t="inlineStr">
-        <is>
-          <t>1.56/3.55/4.85</t>
-        </is>
-      </c>
-      <c r="G126" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H126" s="12" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I126" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J126" s="12" t="inlineStr">
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5807,32 +5807,32 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>周日017</t>
+          <t>周日005</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>荷甲</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>阿贾克斯</t>
+          <t>维罗纳</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>乌德勒支</t>
+          <t>科莫</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>1.49/4.25/4.50</t>
+          <t>8.25/4.65/1.26</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>让+1盘</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>周日019</t>
+          <t>周日009</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
@@ -5867,17 +5867,17 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>西汉姆联</t>
+          <t>伯恩利</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>阿森纳</t>
+          <t>维拉</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>5.40/4.10/1.43</t>
+          <t>5.30/4.00/1.45</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
@@ -5904,70 +5904,70 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>📋 任选9方案（7胆+2双=4注=8元）</t>
+          <t>📋 任选9方案（6胆+3双=8注=16元）</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日004 千叶市原vs町田泽维 → 客胜/平局 (信心6/10)</t>
+          <t>⬜ 周日002 大阪钢巴vs广岛三箭 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜 (信心6/10)</t>
+          <t>⬜ 周日003 柏太阳神vs川崎前锋 → 主胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日013 佛罗伦萨vs热那亚 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日004 千叶市原vs町田泽维 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日015 毕尔巴鄂vs巴伦西亚 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日012 克雷莫纳vs比萨 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日020 科隆vs海登海姆 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日013 佛罗伦萨vs热那亚 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日025 AC米兰vs亚特兰大 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日015 毕尔巴鄂vs巴伦西亚 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日026 巴萨vs皇马 → 主胜 (信心6/10)</t>
+          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周日001 蔚山现代vs富川FC → 主胜/平局 (信心5/10)</t>
+          <t>⬜ 周日020 科隆vs海登海姆 → 主胜 (信心6/10)</t>
         </is>
       </c>
     </row>
@@ -6016,13 +6016,13 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006</t>
+          <t>周日002+周日003</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)</t>
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>1.66×1.89=3.14</t>
+          <t>1.92×1.90=3.65</t>
         </is>
       </c>
     </row>
@@ -6052,14 +6052,14 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013</t>
+          <t>周日002+周日003+周日004</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)</t>
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)
+·千叶市原:客胜(1.75)</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>1.66×1.89×1.89=5.93</t>
+          <t>1.92×1.90×1.75=6.38</t>
         </is>
       </c>
     </row>
@@ -6089,15 +6089,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015</t>
+          <t>周日002+周日003+周日004+周日006</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)
-·毕尔巴鄂:主胜(1.60)</t>
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)
+·千叶市原:客胜(1.75)
+·杜塞多夫:客胜(1.89)</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>1.66×1.89×1.89×1.60=9.49</t>
+          <t>1.92×1.90×1.75×1.89=12.07</t>
         </is>
       </c>
     </row>
@@ -6127,16 +6127,16 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015+周日016</t>
+          <t>周日002+周日003+周日004+周日006+周日012</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)
+·千叶市原:客胜(1.75)
 ·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)
-·毕尔巴鄂:主胜(1.60)
-·费耶诺德:主胜(1.65)</t>
+·克雷莫纳:主胜(1.58)</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>1.66×1.89×1.89×1.60×1.65=15.65</t>
+          <t>1.92×1.90×1.75×1.89×1.58=19.06</t>
         </is>
       </c>
     </row>
@@ -6166,17 +6166,17 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015+周日016+周日020</t>
+          <t>周日002+周日003+周日004+周日006+周日012+周日013</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)
+·千叶市原:客胜(1.75)
 ·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)
-·毕尔巴鄂:主胜(1.60)
-·费耶诺德:主胜(1.65)
-·科隆:主胜(1.90)</t>
+·克雷莫纳:主胜(1.58)
+·佛罗伦萨:主胜(1.89)</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>36.03</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>1.66×1.89×1.89×1.60×1.65×1.90=29.74</t>
+          <t>1.92×1.90×1.75×1.89×1.58×1.89=36.03</t>
         </is>
       </c>
     </row>
@@ -6373,9 +6373,9 @@
         <is>
           <t xml:space="preserve">时间：13:00
 联赛：韩职
-竞彩SP：1.49 / 3.62 / 5.50
-让球SP(真实)：2.79/3.12/2.22
-差值分析：P主=220% P平=90% P客=60%
+竞彩SP：1.51 / 3.55 / 5.40
+让球SP(真实)：2.86/3.12/2.18
+差值分析：P主=216% P平=92% P客=60%
 推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6393,10 +6393,10 @@
         <is>
           <t xml:space="preserve">时间：14:00
 联赛：日职
-竞彩SP：3.12 / 3.30 / 1.98
-让球SP(真实)：1.62/3.70/4.15
-差值分析：P主=106% P平=100% P客=167%
-推荐：客胜 信心2/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:平胜
+竞彩SP：3.45 / 3.14 / 1.92
+让球SP(真实)：1.66/3.62/4.00
+差值分析：P主=91% P平=100% P客=164%
+推荐：客胜 信心6/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6413,10 +6413,10 @@
         <is>
           <t xml:space="preserve">时间：15:00
 联赛：日职
-竞彩SP：2.04 / 3.30 / 2.98
-让球SP(真实)：4.05/3.95/1.59
-差值分析：P主=162% P平=100% P客=111%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+竞彩SP：1.90 / 3.35 / 3.28
+让球SP(真实)：3.75/3.75/1.68
+差值分析：P主=176% P平=100% P客=102%
+推荐：主胜 信心6/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6433,10 +6433,10 @@
         <is>
           <t xml:space="preserve">时间：16:00
 联赛：日职
-竞彩SP：4.30 / 3.40 / 1.66
-让球SP(真实)：1.96/3.21/3.25
-差值分析：P主=79% P平=100% P客=205%
-推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:负负
+竞彩SP：4.00 / 3.25 / 1.75
+让球SP(真实)：1.83/3.20/3.70
+差值分析：P主=81% P平=100% P客=186%
+推荐：客胜 信心6/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6454,7 +6454,7 @@
           <t xml:space="preserve">时间：18:30
 联赛：意甲
 竞彩SP：8.25 / 4.65 / 1.26
-让球SP(真实)：3.02/3.40/1.99
+让球SP(真实)：3.12/3.32/1.97
 差值分析：P主=42% P平=74% P客=273%
 推荐：客胜 信心5/10 比分1-2(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
@@ -6476,7 +6476,7 @@
 竞彩SP：3.02 / 3.72 / 1.89
 让球SP(真实)：1.70/4.00/3.43
 差值分析：P主=119% P平=96% P客=190%
-推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(43%) 备选半全场:负负
+推荐：客胜 信心6/10 比分0-1(泊松) 半全场负负 大小球小2.5(43%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6493,9 +6493,9 @@
         <is>
           <t xml:space="preserve">时间：20:00
 联赛：西甲
-竞彩SP：2.15 / 3.40 / 2.70
-让球SP(真实)：4.45/4.00/1.53
-差值分析：P主=158% P平=100% P客=126%
+竞彩SP：2.20 / 3.40 / 2.63
+让球SP(真实)：4.68/3.95/1.51
+差值分析：P主=155% P平=100% P客=129%
 推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6516,7 +6516,7 @@
 竞彩SP：2.52 / 3.45 / 2.26
 让球SP(真实)：1.49/4.05/4.75
 差值分析：P主=137% P平=100% P客=153%
-推荐：不投 信心2/10 比分1-1(泊松) 半全场平胜 大小球小2.5(42%) 备选半全场:胜胜
+推荐：不投 信心2/10 比分1-1(泊松) 半全场— 大小球小2.5(42%) 备选半全场:—
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6533,9 +6533,9 @@
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：5.10 / 3.95 / 1.47
-让球SP(真实)：2.32/3.40/2.48
-差值分析：P主=73% P平=95% P客=255%
+竞彩SP：5.30 / 4.00 / 1.45
+让球SP(真实)：2.35/3.40/2.44
+差值分析：P主=71% P平=94% P客=259%
 推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6553,10 +6553,10 @@
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：2.65 / 3.15 / 2.30
-让球SP(真实)：1.45/4.05/5.20
-差值分析：P主=119% P平=100% P客=137%
-推荐：客胜 信心2/10 比分1-2(泊松) 半全场胜胜 大小球大2.5(64%) 备选半全场:平胜
+竞彩SP：2.73 / 3.05 / 2.30
+让球SP(真实)：1.47/3.95/5.10
+差值分析：P主=112% P平=100% P客=133%
+推荐：客胜 信心2/10 比分1-2(泊松) 半全场负负 大小球大2.5(64%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6576,7 +6576,7 @@
 竞彩SP：2.57 / 3.32 / 2.28
 让球SP(真实)：1.46/4.20/4.85
 差值分析：P主=129% P平=100% P客=146%
-推荐：不投 信心2/10 比分2-2(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
+推荐：不投 信心2/10 比分2-2(泊松) 半全场— 大小球大2.5(67%) 备选半全场:—
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6593,10 +6593,10 @@
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：意甲
-竞彩SP：1.56 / 3.55 / 4.85
-让球SP(真实)：2.90/3.25/2.10
-差值分析：P主=209% P平=92% P客=67%
-推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
+竞彩SP：1.58 / 3.50 / 4.75
+让球SP(真实)：3.00/3.25/2.05
+差值分析：P主=206% P平=93% P客=68%
+推荐：主胜 信心6/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6613,9 +6613,9 @@
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：意甲
-竞彩SP：1.89 / 3.15 / 3.55
+竞彩SP：1.89 / 3.08 / 3.63
 让球SP(真实)：4.05/3.50/1.68
-差值分析：P主=167% P平=100% P客=89%
+差值分析：P主=163% P平=100% P客=85%
 推荐：主胜 信心6/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6636,7 +6636,7 @@
 竞彩SP：2.46 / 3.45 / 2.31
 让球SP(真实)：1.47/4.15/4.80
 差值分析：P主=140% P平=100% P客=149%
-推荐：不投 信心2/10 比分1-1(泊松) 半全场平胜 大小球小2.5(45%) 备选半全场:胜胜
+推荐：不投 信心2/10 比分1-1(泊松) 半全场— 大小球小2.5(45%) 备选半全场:—
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6673,9 +6673,9 @@
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
-竞彩SP：1.65 / 3.95 / 3.70
-让球SP(真实)：2.80/3.90/1.94
-差值分析：P主=220% P平=92% P客=98%
+竞彩SP：1.68 / 3.90 / 3.60
+让球SP(真实)：2.95/3.80/1.90
+差值分析：P主=216% P平=93% P客=101%
 推荐：主胜 信心6/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(48%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6716,7 +6716,7 @@
 竞彩SP：2.74 / 3.65 / 2.04
 让球SP(真实)：1.58/4.05/4.00
 差值分析：P主=130% P平=98% P客=175%
-推荐：客胜 信心2/10 比分1-2(泊松) 半全场平负 大小球大2.5(58%) 备选半全场:平胜
+推荐：客胜 信心2/10 比分1-2(泊松) 半全场负负 大小球大2.5(58%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6733,9 +6733,9 @@
         <is>
           <t xml:space="preserve">时间：23:30
 联赛：英超
-竞彩SP：5.40 / 4.10 / 1.43
-让球SP(真实)：2.40/3.40/2.40
-差值分析：P主=70% P平=92% P客=264%
+竞彩SP：5.50 / 4.20 / 1.41
+让球SP(真实)：2.45/3.50/2.30
+差值分析：P主=69% P平=90% P客=269%
 推荐：客胜 信心5/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6773,9 +6773,9 @@
         <is>
           <t xml:space="preserve">时间：00:00
 联赛：意甲
-竞彩SP：6.25 / 4.10 / 1.38
-让球SP(真实)：2.50/3.25/2.37
-差值分析：P主=54% P平=82% P客=244%
+竞彩SP：6.42 / 4.10 / 1.37
+让球SP(真实)：2.55/3.25/2.33
+差值分析：P主=52% P平=82% P客=246%
 推荐：客胜 信心5/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:胜负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6796,7 +6796,7 @@
 竞彩SP：2.79 / 2.70 / 2.50
 让球SP(真实)：1.39/3.80/6.80
 差值分析：P主=76% P平=79% P客=85%
-推荐：平局 信心2/10 比分1-1(泊松) 半全场平胜 大小球小2.5(43%) 备选半全场:胜胜
+推荐：平局 信心2/10 比分1-1(泊松) 半全场平平 大小球小2.5(43%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6833,10 +6833,10 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙职
-竞彩SP：1.30 / 4.60 / 7.00
-让球SP(真实)：2.03/3.43/2.90
-差值分析：P主=343% P平=97% P客=64%
-推荐：主胜 信心7/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(47%) 备选半全场:平胜
+竞彩SP：1.32 / 4.50 / 6.70
+让球SP(真实)：2.08/3.43/2.80
+差值分析：P主=337% P平=99% P客=66%
+推荐：主胜 信心7/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6854,7 +6854,7 @@
           <t xml:space="preserve">时间：02:45
 联赛：意甲
 竞彩SP：1.90 / 3.28 / 3.35
-让球SP(真实)：3.85/3.65/1.68
+让球SP(真实)：3.90/3.60/1.68
 差值分析：P主=168% P平=97% P客=95%
 推荐：主胜 信心6/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:负胜
 让球:让-1 输盘=让平/让负 </t>
@@ -6876,7 +6876,7 @@
 竞彩SP：1.51 / 4.65 / 3.96
 让球SP(真实)：2.40/3.85/2.21
 差值分析：P主=241% P平=78% P客=92%
-推荐：主胜 信心6/10 比分3-2(泊松) 半全场负负 大小球大2.5(71%) 备选半全场:胜负
+推荐：主胜 信心6/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6893,10 +6893,10 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：法甲
-竞彩SP：2.22 / 3.20 / 2.73
-让球SP(真实)：4.95/3.85/1.50
-差值分析：P主=144% P平=100% P客=117%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场平胜 大小球小2.5(42%) 备选半全场:胜胜
+竞彩SP：2.23 / 3.15 / 2.75
+让球SP(真实)：5.00/3.88/1.49
+差值分析：P主=141% P平=100% P客=115%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6933,9 +6933,9 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：法甲
-竞彩SP：2.14 / 3.60 / 2.60
-让球SP(真实)：4.45/4.00/1.53
-差值分析：P主=166% P平=99% P客=137%
+竞彩SP：2.19 / 3.55 / 2.56
+让球SP(真实)：4.60/4.00/1.51
+差值分析：P主=162% P平=100% P客=138%
 推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:负胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6953,10 +6953,10 @@
         <is>
           <t xml:space="preserve">时间：04:30
 联赛：美职
-竞彩SP：2.23 / 3.40 / 2.59
-让球SP(真实)：4.80/4.00/1.49
-差值分析：P主=152% P平=100% P客=131%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场平胜 大小球小2.5(43%) 备选半全场:胜胜
+竞彩SP：2.25 / 3.35 / 2.59
+让球SP(真实)：4.75/3.97/1.50
+差值分析：P主=149% P平=100% P客=129%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6964,8 +6964,8 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A123:B123"/>
     <mergeCell ref="A1:B1"/>
@@ -7082,13 +7082,13 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006</t>
+          <t>周日002+周日003</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)</t>
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>6.28元</t>
+          <t>7.30元</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>3.14倍</t>
+          <t>3.65倍</t>
         </is>
       </c>
     </row>
@@ -7118,14 +7118,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013</t>
+          <t>周日002+周日003+周日004</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)</t>
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)
+·千叶市原:客胜(1.75)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>11.86元</t>
+          <t>12.76元</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>5.93倍</t>
+          <t>6.38倍</t>
         </is>
       </c>
     </row>
@@ -7155,15 +7155,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015</t>
+          <t>周日002+周日003+周日004+周日006</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
-·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)
-·毕尔巴鄂:主胜(1.60)</t>
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)
+·千叶市原:客胜(1.75)
+·杜塞多夫:客胜(1.89)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>18.98元</t>
+          <t>24.14元</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>9.49倍</t>
+          <t>12.07倍</t>
         </is>
       </c>
     </row>
@@ -7193,16 +7193,16 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015+周日016</t>
+          <t>周日002+周日003+周日004+周日006+周日012</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)
+·千叶市原:客胜(1.75)
 ·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)
-·毕尔巴鄂:主胜(1.60)
-·费耶诺德:主胜(1.65)</t>
+·克雷莫纳:主胜(1.58)</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>31.30元</t>
+          <t>38.12元</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>15.65倍</t>
+          <t>19.06倍</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015+周日016+周日020</t>
+          <t>周日002+周日003+周日004+周日006+周日012+周日013</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)
+          <t>·大阪钢巴:客胜(1.92)
+·柏太阳神:主胜(1.90)
+·千叶市原:客胜(1.75)
 ·杜塞多夫:客胜(1.89)
-·佛罗伦萨:主胜(1.89)
-·毕尔巴鄂:主胜(1.60)
-·费耶诺德:主胜(1.65)
-·科隆:主胜(1.90)</t>
+·克雷莫纳:主胜(1.58)
+·佛罗伦萨:主胜(1.89)</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>59.48元</t>
+          <t>72.06元</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>29.74倍</t>
+          <t>36.03倍</t>
         </is>
       </c>
     </row>
@@ -7284,13 +7284,13 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006</t>
+          <t>周日002+周日003</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:0-1(8.3)
-·杜塞多夫:0-1(9.4)</t>
+          <t>·大阪钢巴:0-1(9.6)
+·柏太阳神:1-0(9.5)</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>约157元</t>
+          <t>约182元</t>
         </is>
       </c>
     </row>
@@ -7325,14 +7325,14 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013</t>
+          <t>周日002+周日003+周日004</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:0-1(8.3)
-·杜塞多夫:0-1(9.4)
-·佛罗伦萨:2-1(9.4)</t>
+          <t>·大阪钢巴:0-1(9.6)
+·柏太阳神:1-0(9.5)
+·千叶市原:0-1(8.8)</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>798</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>约1482元</t>
+          <t>约1596元</t>
         </is>
       </c>
     </row>
@@ -7381,14 +7381,14 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013</t>
+          <t>周日002+周日003+周日004</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)/让平/让负
-·杜塞多夫:客胜(1.89)/让平/让负
-·佛罗伦萨:主胜(1.89)/让平/让负</t>
+          <t>·大阪钢巴:客胜(1.92)/让平/让负
+·柏太阳神:主胜(1.90)/让平/让负
+·千叶市原:客胜(1.75)/让平/让负</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>11.86元</t>
+          <t>12.77元</t>
         </is>
       </c>
     </row>
@@ -7423,15 +7423,15 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015</t>
+          <t>周日002+周日003+周日004+周日006</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:客胜(1.66)/让平/让负
-·杜塞多夫:客胜(1.89)/让平/让负
-·佛罗伦萨:主胜(1.89)/让平/让负
-·毕尔巴鄂:主胜(1.60)/让平/让负</t>
+          <t>·大阪钢巴:客胜(1.92)/让平/让负
+·柏太阳神:主胜(1.90)/让平/让负
+·千叶市原:客胜(1.75)/让平/让负
+·杜塞多夫:客胜(1.89)/让平/让负</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>18.97元</t>
+          <t>24.13元</t>
         </is>
       </c>
     </row>
@@ -7480,13 +7480,13 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006</t>
+          <t>周日002+周日003</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:平负(3.5)
-·杜塞多夫:平负(3.5)</t>
+          <t>·大阪钢巴:负负(2.5)
+·柏太阳神:胜胜(2.2)</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>24.50元</t>
+          <t>11.00元</t>
         </is>
       </c>
     </row>
@@ -7521,14 +7521,14 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013</t>
+          <t>周日002+周日003+周日004</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:平负(3.5)
-·杜塞多夫:平负(3.5)
-·佛罗伦萨:胜胜(2.2)</t>
+          <t>·大阪钢巴:负负(2.5)
+·柏太阳神:胜胜(2.2)
+·千叶市原:负负(2.5)</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>53.90元</t>
+          <t>27.50元</t>
         </is>
       </c>
     </row>
@@ -7563,15 +7563,15 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015</t>
+          <t>周日002+周日003+周日004+周日006</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:平负(3.5)
-·杜塞多夫:平负(3.5)
-·佛罗伦萨:胜胜(2.2)
-·毕尔巴鄂:胜胜(2.2)</t>
+          <t>·大阪钢巴:负负(2.5)
+·柏太阳神:胜胜(2.2)
+·千叶市原:负负(2.5)
+·杜塞多夫:负负(2.5)</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>34.38</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>118.58元</t>
+          <t>68.75元</t>
         </is>
       </c>
     </row>
@@ -7606,16 +7606,16 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015+周日016</t>
+          <t>周日002+周日003+周日004+周日006+周日012</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:平负(3.5)
-·杜塞多夫:平负(3.5)
-·佛罗伦萨:胜胜(2.2)
-·毕尔巴鄂:胜胜(2.2)
-·费耶诺德:胜胜(2.2)</t>
+          <t>·大阪钢巴:负负(2.5)
+·柏太阳神:胜胜(2.2)
+·千叶市原:负负(2.5)
+·杜塞多夫:负负(2.5)
+·克雷莫纳:胜胜(2.2)</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>130.44</t>
+          <t>75.62</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>260.88元</t>
+          <t>151.25元</t>
         </is>
       </c>
     </row>
@@ -7650,17 +7650,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>周日004+周日006+周日013+周日015+周日016+周日020</t>
+          <t>周日002+周日003+周日004+周日006+周日012+周日013</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>·千叶市原:平负(3.5)
-·杜塞多夫:平负(3.5)
-·佛罗伦萨:胜胜(2.2)
-·毕尔巴鄂:胜胜(2.2)
-·费耶诺德:胜胜(2.2)
-·科隆:胜胜(2.2)</t>
+          <t>·大阪钢巴:负负(2.5)
+·柏太阳神:胜胜(2.2)
+·千叶市原:负负(2.5)
+·杜塞多夫:负负(2.5)
+·克雷莫纳:胜胜(2.2)
+·佛罗伦萨:胜胜(2.2)</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>286.96</t>
+          <t>166.38</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>573.93元</t>
+          <t>332.75元</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-10.xlsx
+++ b/Aii竞彩推荐_2026-05-10.xlsx
@@ -94,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -116,55 +116,11 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,17 +145,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,11 +154,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -577,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -595,14 +537,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🌍 2026-05-10 周日30场竞彩推荐+14场胜负彩(查lottery.gov.cn期号)</t>
+          <t>🌍 2026-05-10 周日30场竞彩推荐（今天无14场奖期）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:54</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 19:10</t>
         </is>
       </c>
     </row>
@@ -623,7 +565,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2025-26赛季末段，保级+欧战争夺激烈。30场竞彩+14场(需查lottery.gov.cn官方奖期)。</t>
+          <t>2025-26赛季末段，保级+欧战争夺激烈。30场竞彩。</t>
         </is>
       </c>
     </row>
@@ -952,7 +894,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP3.10/3.72/1.86 让球+1</t>
+          <t>SP3.06/3.65/1.89 让球+1</t>
         </is>
       </c>
     </row>
@@ -999,7 +941,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.30/3.40/2.50 让球-1</t>
+          <t>SP2.15/3.40/2.70 让球-1</t>
         </is>
       </c>
     </row>
@@ -1046,7 +988,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP2.52/3.45/2.26 让球+1</t>
+          <t>SP2.45/3.45/2.32 让球+1</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1035,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP5.50/4.20/1.41 让球+1</t>
+          <t>SP5.75/4.23/1.39 让球+1</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1129,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>SP2.65/3.32/2.22 让球+1</t>
+          <t>SP2.70/3.33/2.18 让球+1</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1317,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>SP1.54/3.57/5.00 让球-1</t>
+          <t>SP1.52/3.58/5.20 让球-1</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1411,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>SP1.43/4.35/5.00 让球-1</t>
+          <t>SP1.41/4.50/5.05 让球-1</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1458,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>SP2.74/3.65/2.04 让球+1</t>
+          <t>SP2.77/3.70/2.01 让球+1</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1505,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>SP5.70/4.26/1.39 让球+1</t>
+          <t>SP5.80/4.40/1.37 让球+1</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1599,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>SP6.42/4.10/1.37 让球+1</t>
+          <t>SP6.65/4.20/1.35 让球+1</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1693,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>SP1.58/3.80/4.28 让球-1</t>
+          <t>SP1.55/3.80/4.55 让球-1</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1787,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>SP1.94/3.22/3.30 让球-1</t>
+          <t>SP1.94/3.15/3.37 让球-1</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1881,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>SP2.23/3.15/2.75 让球-1</t>
+          <t>SP2.25/3.05/2.80 让球-1</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2029,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 17:54）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 19:10）</t>
         </is>
       </c>
     </row>
@@ -2390,13 +2332,13 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -2405,7 +2347,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2415,7 +2357,7 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -2436,32 +2378,32 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>3.4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J51" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>1.53</t>
         </is>
       </c>
     </row>
@@ -2482,13 +2424,13 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>3.45</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -2497,17 +2439,17 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.90</t>
         </is>
       </c>
     </row>
@@ -2528,13 +2470,13 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -2543,17 +2485,17 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.34</t>
         </is>
       </c>
     </row>
@@ -2620,13 +2562,13 @@
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -2635,17 +2577,17 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.47</t>
         </is>
       </c>
     </row>
@@ -2804,13 +2746,13 @@
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -2824,12 +2766,12 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
@@ -2896,13 +2838,13 @@
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -2911,7 +2853,7 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -2921,7 +2863,7 @@
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
     </row>
@@ -2942,13 +2884,13 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2957,17 +2899,17 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.93</t>
         </is>
       </c>
     </row>
@@ -2988,13 +2930,13 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>4.26</v>
+        <v>4.4</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -3003,17 +2945,17 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
@@ -3080,13 +3022,13 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>6.42</v>
+        <v>6.65</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -3095,12 +3037,12 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
@@ -3172,13 +3114,13 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>4.28</v>
+        <v>4.55</v>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
@@ -3187,17 +3129,17 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.12</t>
         </is>
       </c>
     </row>
@@ -3267,10 +3209,10 @@
         <v>1.94</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
@@ -3279,12 +3221,12 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
@@ -3356,13 +3298,13 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
@@ -3600,7 +3542,7 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -3630,7 +3572,7 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=216%P平=92%P客=60%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=48%P平=28%P客=24%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3594,7 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3682,7 +3624,7 @@
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=91%P平=100%P客=164%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=34%P平=30%P客=36%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3646,7 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3734,7 +3676,7 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=176%P平=100%P客=102%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=43%P平=29%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3698,7 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -3786,7 +3728,7 @@
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=81%P平=100%P客=186%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=33%P平=30%P客=37%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3750,7 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -3838,7 +3780,7 @@
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=40%P平=73%P客=276%|泊松比分1-2|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=32%P平=27%P客=41%|泊松比分1-2|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3802,7 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -3890,111 +3832,111 @@
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=116%P平=96%P客=193%|泊松比分0-1|半全场平负|大小球小2.5(43%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=35%P平=29%P客=36%|泊松比分0-1|半全场平负|大小球小2.5(43%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>周日007</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>马洛卡vs比利亚雷</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=148%P平=100%P客=136%|泊松比分1-1|半全场平胜|大小球小2.5(44%)|让球-1=输盘/让平/让负|放弃</t>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=41%P平=28%P客=31%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>周日008</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>罗森博格vs利勒斯特</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J87" s="10" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=137%P平=100%P客=153%|泊松比分1-1|半全场平胜|大小球小2.5(42%)|让球+1=输盘/让平/让负|放弃</t>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=37%P平=30%P客=33%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4016,7 +3958,7 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -4046,59 +3988,59 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=69%P平=90%P客=269%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=31%P平=27%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>周日010</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>水晶宫vs埃弗顿</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>平平</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>平负</t>
-        </is>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J89" s="11" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=95%P平=90%P客=120%|泊松比分1-1|半全场胜胜|大小球小2.5(52%)|让球+1=输盘/让平/让负|平SP低+联赛特征</t>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=37%P平=30%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(64%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4115,17 +4057,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -4135,12 +4077,12 @@
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>负胜</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
@@ -4150,7 +4092,7 @@
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=125%P平=100%P客=150%|泊松比分1-2|半全场胜胜|大小球大2.5(67%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=36%P平=28%P客=35%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4114,7 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -4202,7 +4144,7 @@
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=202%P平=94%P客=70%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=46%P平=28%P客=26%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4166,7 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -4254,59 +4196,59 @@
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=143%P平=90%P客=72%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=43%P平=29%P客=28%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>周日014</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>汉堡vs弗赖堡</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J93" s="10" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=133%P平=100%P客=145%|泊松比分1-1|半全场平胜|大小球小2.5(45%)|让球+1=输盘/让平/让负|放弃</t>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=37%P平=30%P客=33%|泊松比分2-1|半全场平胜|大小球大2.5(57%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4270,7 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -4358,7 +4300,7 @@
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=224%P平=97%P客=69%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=48%P平=27%P客=25%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4322,7 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -4410,7 +4352,7 @@
       </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=210%P平=95%P客=102%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4404,7 @@
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=259%P平=85%P客=74%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=53%P平=25%P客=22%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4479,32 +4421,32 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -4514,7 +4456,7 @@
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=130%P平=98%P客=175%|泊松比分1-2|半全场平负|大小球大2.5(58%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=37%P平=28%P客=35%|泊松比分2-1|半全场平负|大小球大2.5(58%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4478,7 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -4566,7 +4508,7 @@
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=67%P平=89%P客=274%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=29%P平=26%P客=45%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4530,7 @@
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -4618,7 +4560,7 @@
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=190%P平=100%P客=127%|泊松比分1-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4582,7 @@
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -4670,59 +4612,59 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=52%P平=82%P客=246%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=32%P平=27%P客=41%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>周日022</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>奥维耶多vs赫塔费</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>2/10</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>平平</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>平负</t>
-        </is>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J101" s="11" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=76%P平=79%P客=85%|泊松比分1-1|半全场平胜|大小球小2.5(43%)|让球+1=输盘/让平/让负|平SP低+联赛特征</t>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=39%P平=30%P客=31%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4686,7 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -4774,59 +4716,59 @@
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=235%P平=98%P客=87%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>周日024</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>吉达联合vs达马克</t>
         </is>
       </c>
-      <c r="C103" s="12" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="F103" s="12" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <t>3-0</t>
         </is>
       </c>
-      <c r="G103" s="12" t="inlineStr">
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H103" s="12" t="inlineStr">
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I103" s="12" t="inlineStr">
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J103" s="13" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=337%P平=99%P客=66%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=50%P平=26%P客=24%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4790,7 @@
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -4878,7 +4820,7 @@
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=164%P平=99%P客=96%|泊松比分3-2|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=41%P平=27%P客=31%|泊松比分3-2|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4842,7 @@
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -4930,7 +4872,7 @@
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=241%P平=78%P客=92%|泊松比分3-2|半全场负负|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=43%P平=25%P客=32%|泊松比分3-2|半全场负负|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4894,7 @@
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -4982,59 +4924,59 @@
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=141%P平=100%P客=115%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=40%P平=30%P客=30%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>周日028</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>巴黎圣曼vs布雷斯特</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>1/10</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H107" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I107" s="7" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J107" s="10" t="inlineStr">
-        <is>
-          <t>无有效SP数据，跳过</t>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=38%P平=31%P客=31%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球-2=输盘/让平/让负⚠️让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
@@ -5056,7 +4998,7 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -5086,7 +5028,7 @@
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=155%P平=100%P客=135%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5050,7 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -5138,7 +5080,7 @@
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=149%P平=100%P客=129%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=41%P平=29%P客=30%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5202,100 +5144,100 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="n">
+      <c r="A115" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>周日002</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>日职</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>大阪钢巴</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>广岛三箭</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>3.45/3.14/1.92</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H115" s="6" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J115" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>周日016</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>荷甲</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>费耶诺德</t>
+        </is>
+      </c>
+      <c r="E115" s="10" t="inlineStr">
+        <is>
+          <t>阿尔克马</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>1.72/3.80/3.52</t>
+        </is>
+      </c>
+      <c r="G115" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="I115" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J115" s="10" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="n">
+      <c r="A116" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>周日003</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>日职</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>柏太阳神</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>川崎前锋</t>
-        </is>
-      </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>1.90/3.35/3.28</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J116" s="6" t="inlineStr">
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>周日017</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>荷甲</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>阿贾克斯</t>
+        </is>
+      </c>
+      <c r="E116" s="10" t="inlineStr">
+        <is>
+          <t>乌德勒支</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>1.41/4.50/5.05</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J116" s="10" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5307,27 +5249,27 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>周日004</t>
+          <t>周日005</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>日职</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>千叶市原</t>
+          <t>维罗纳</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>町田泽维</t>
+          <t>科莫</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>4.00/3.25/1.75</t>
+          <t>8.55/4.70/1.25</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
@@ -5337,7 +5279,7 @@
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr">
@@ -5352,300 +5294,300 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="12" t="n">
+      <c r="A118" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>周日006</t>
         </is>
       </c>
-      <c r="C118" s="12" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>德乙</t>
         </is>
       </c>
-      <c r="D118" s="12" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>杜塞多夫</t>
         </is>
       </c>
-      <c r="E118" s="12" t="inlineStr">
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>埃沃斯堡</t>
         </is>
       </c>
-      <c r="F118" s="12" t="inlineStr">
-        <is>
-          <t>3.10/3.72/1.86</t>
-        </is>
-      </c>
-      <c r="G118" s="12" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H118" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I118" s="12" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>3.06/3.65/1.89</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>让+1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>周日007</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>马洛卡</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>比利亚雷</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>2.15/3.40/2.70</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>周日009</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>伯恩利</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>维拉</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>5.75/4.23/1.39</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>让+1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>周日012</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>克雷莫纳</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>比萨</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>1.60/3.45/4.65</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J118" s="12" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B119" s="12" t="inlineStr">
-        <is>
-          <t>周日012</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>周日013</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>意甲</t>
         </is>
       </c>
-      <c r="D119" s="12" t="inlineStr">
-        <is>
-          <t>克雷莫纳</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>比萨</t>
-        </is>
-      </c>
-      <c r="F119" s="12" t="inlineStr">
-        <is>
-          <t>1.60/3.45/4.65</t>
-        </is>
-      </c>
-      <c r="G119" s="12" t="inlineStr">
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>佛罗伦萨</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>热那亚</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>1.89/3.00/3.74</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>让-1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>周日015</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>毕尔巴鄂</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>巴伦西亚</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>1.52/3.58/5.20</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="H119" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I119" s="12" t="inlineStr">
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I123" s="10" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J119" s="12" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B120" s="12" t="inlineStr">
-        <is>
-          <t>周日016</t>
-        </is>
-      </c>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D120" s="12" t="inlineStr">
-        <is>
-          <t>费耶诺德</t>
-        </is>
-      </c>
-      <c r="E120" s="12" t="inlineStr">
-        <is>
-          <t>阿尔克马</t>
-        </is>
-      </c>
-      <c r="F120" s="12" t="inlineStr">
-        <is>
-          <t>1.72/3.80/3.52</t>
-        </is>
-      </c>
-      <c r="G120" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H120" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I120" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J120" s="12" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B121" s="12" t="inlineStr">
-        <is>
-          <t>周日020</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="inlineStr">
-        <is>
-          <t>德甲</t>
-        </is>
-      </c>
-      <c r="D121" s="12" t="inlineStr">
-        <is>
-          <t>科隆</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>海登海姆</t>
-        </is>
-      </c>
-      <c r="F121" s="12" t="inlineStr">
-        <is>
-          <t>1.94/3.70/2.91</t>
-        </is>
-      </c>
-      <c r="G121" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I121" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J121" s="12" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B122" s="12" t="inlineStr">
-        <is>
-          <t>周日025</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D122" s="12" t="inlineStr">
-        <is>
-          <t>AC米兰</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>亚特兰大</t>
-        </is>
-      </c>
-      <c r="F122" s="12" t="inlineStr">
-        <is>
-          <t>1.94/3.22/3.30</t>
-        </is>
-      </c>
-      <c r="G122" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I122" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J122" s="12" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B123" s="12" t="inlineStr">
-        <is>
-          <t>周日026</t>
-        </is>
-      </c>
-      <c r="C123" s="12" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D123" s="12" t="inlineStr">
-        <is>
-          <t>巴萨</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>皇马</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>1.51/4.65/3.96</t>
-        </is>
-      </c>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H123" s="12" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
-      </c>
-      <c r="I123" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J123" s="12" t="inlineStr">
+      <c r="J123" s="10" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5657,27 +5599,27 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>周日001</t>
+          <t>周日018</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>荷甲</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>蔚山现代</t>
+          <t>格罗宁根</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>富川FC</t>
+          <t>奈梅亨</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>1.51/3.55/5.40</t>
+          <t>2.77/3.70/2.01</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5687,7 +5629,7 @@
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
@@ -5697,205 +5639,205 @@
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
+          <t>让+1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>周日019</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>西汉姆联</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>阿森纳</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>5.80/4.40/1.37</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>让+1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>周日020</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>科隆</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>海登海姆</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>1.94/3.70/2.91</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
           <t>让-1盘</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B125" s="12" t="inlineStr">
-        <is>
-          <t>周日005</t>
-        </is>
-      </c>
-      <c r="C125" s="12" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>周日021</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>意甲</t>
         </is>
       </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t>维罗纳</t>
-        </is>
-      </c>
-      <c r="E125" s="12" t="inlineStr">
-        <is>
-          <t>科莫</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="inlineStr">
-        <is>
-          <t>8.55/4.70/1.25</t>
-        </is>
-      </c>
-      <c r="G125" s="12" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I125" s="12" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>帕尔马</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>6.65/4.20/1.35</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>让+1盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>周日023</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>美因茨</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>柏林联合</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>1.55/3.80/4.55</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J125" s="12" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B126" s="12" t="inlineStr">
-        <is>
-          <t>周日009</t>
-        </is>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="D126" s="12" t="inlineStr">
-        <is>
-          <t>伯恩利</t>
-        </is>
-      </c>
-      <c r="E126" s="12" t="inlineStr">
-        <is>
-          <t>维拉</t>
-        </is>
-      </c>
-      <c r="F126" s="12" t="inlineStr">
-        <is>
-          <t>5.50/4.20/1.41</t>
-        </is>
-      </c>
-      <c r="G126" s="12" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H126" s="12" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I126" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J126" s="12" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B127" s="12" t="inlineStr">
-        <is>
-          <t>周日015</t>
-        </is>
-      </c>
-      <c r="C127" s="12" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D127" s="12" t="inlineStr">
-        <is>
-          <t>毕尔巴鄂</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>巴伦西亚</t>
-        </is>
-      </c>
-      <c r="F127" s="12" t="inlineStr">
-        <is>
-          <t>1.54/3.57/5.00</t>
-        </is>
-      </c>
-      <c r="G127" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I127" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J127" s="12" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="B128" s="12" t="inlineStr">
-        <is>
-          <t>周日017</t>
-        </is>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D128" s="12" t="inlineStr">
-        <is>
-          <t>阿贾克斯</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>乌德勒支</t>
-        </is>
-      </c>
-      <c r="F128" s="12" t="inlineStr">
-        <is>
-          <t>1.43/4.35/5.00</t>
-        </is>
-      </c>
-      <c r="G128" s="12" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I128" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J128" s="12" t="inlineStr">
+      <c r="J128" s="10" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5904,70 +5846,70 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>📋 任选9方案（6胆+3双=8注=16元）</t>
+          <t>📋 任选9方案（4胆+5双=32注=64元）</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日002 大阪钢巴vs广岛三箭 → 客胜/平局 (信心6/10)</t>
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜 (信心5/10)</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日003 柏太阳神vs川崎前锋 → 主胜/平局 (信心6/10)</t>
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日017 阿贾克斯vs乌德勒支 → 主胜 (信心5/10)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日004 千叶市原vs町田泽维 → 客胜/平局 (信心6/10)</t>
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日005 维罗纳vs科莫 → 客胜/平局 (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜 (信心6/10)</t>
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜/平局 (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日012 克雷莫纳vs比萨 → 主胜 (信心6/10)</t>
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日007 马洛卡vs比利亚雷 → 主胜/平局 (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜 (信心6/10)</t>
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日009 伯恩利vs维拉 → 客胜/平局 (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日020 科隆vs海登海姆 → 主胜 (信心6/10)</t>
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日012 克雷莫纳vs比萨 → 主胜 (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日025 AC米兰vs亚特兰大 → 主胜 (信心6/10)</t>
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日013 佛罗伦萨vs热那亚 → 主胜/平局 (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="14" t="inlineStr">
-        <is>
-          <t>⬜ 周日026 巴萨vs皇马 → 主胜 (信心6/10)</t>
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>⬜ 周日015 毕尔巴鄂vs巴伦西亚 → 主胜 (信心4/10)</t>
         </is>
       </c>
     </row>
@@ -6016,13 +5958,13 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日003</t>
+          <t>周日016+周日017</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)</t>
+          <t>·费耶诺德:主胜(1.72)
+·阿贾克斯:主胜(1.41)</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
@@ -6035,281 +5977,127 @@
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>1.92×1.90=3.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)
-·千叶市原:客胜(1.75)</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F151" s="6" t="inlineStr">
-        <is>
-          <t>6.38</t>
-        </is>
-      </c>
-      <c r="G151" s="6" t="inlineStr">
-        <is>
-          <t>1.92×1.90×1.75=6.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>4串1</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)
-·千叶市原:客胜(1.75)
-·杜塞多夫:客胜(1.86)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>11.87</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>1.92×1.90×1.75×1.86=11.87</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006+周日012</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)
-·千叶市原:客胜(1.75)
-·杜塞多夫:客胜(1.86)
-·克雷莫纳:主胜(1.60)</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="G153" s="6" t="inlineStr">
-        <is>
-          <t>1.92×1.90×1.75×1.86×1.60=19.00</t>
+          <t>1.72×1.41=2.43</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006+周日012+周日016</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)
-·千叶市原:客胜(1.75)
-·杜塞多夫:客胜(1.86)
-·克雷莫纳:主胜(1.60)
-·费耶诺德:主胜(1.72)</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F154" s="6" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>1.92×1.90×1.75×1.86×1.60×1.72=32.68</t>
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ 核心信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>场次</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>解读</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>应对</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>🟢 高信心(7/10+)</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>015/017/023/024/029</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>5场贝叶斯概率最高，SP均&lt;1.45</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>作胆材/串关核心</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>🟢 让球SP真实数据</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>全部场次</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>从500.com让球页提取，非估算</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>可用作让球分析</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 核心信号</t>
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>🟡 平局候选</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>004/007/011</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>平局概率30-35%，接近主胜</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>双选或慎入</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
-        <is>
-          <t>场次</t>
-        </is>
-      </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>解读</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
-        <is>
-          <t>应对</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="12" t="inlineStr">
-        <is>
-          <t>🟢 高信心(7/10+)</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>015/017/023/024/029</t>
-        </is>
-      </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>5场贝叶斯概率最高，SP均&lt;1.45</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>作胆材/串关核心</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="12" t="inlineStr">
-        <is>
-          <t>🟢 让球SP真实数据</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>🟡 让球数真实</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>从500.com让球页提取，非估算</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>可用作让球分析</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>🟡 平局候选</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>004/007/011</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>平局概率30-35%，接近主胜</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>双选或慎入</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="8" t="inlineStr">
-        <is>
-          <t>🟡 让球数真实</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>全部场次</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
@@ -6330,10 +6118,10 @@
     <mergeCell ref="A78:J78"/>
     <mergeCell ref="A137:J137"/>
     <mergeCell ref="A133:J133"/>
-    <mergeCell ref="A158:J158"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A136:J136"/>
     <mergeCell ref="A139:J139"/>
+    <mergeCell ref="A154:J154"/>
     <mergeCell ref="A113:J113"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
@@ -6355,608 +6143,608 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>📋 2026-05-10 每场完整分析（30场）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日001 蔚山现代 vs 富川FC [韩职] 13:00</t>
         </is>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1">
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：13:00
 联赛：韩职
 竞彩SP：1.51 / 3.55 / 5.40
 让球SP(真实)：2.86/3.12/2.18
-差值分析：P主=216% P平=92% P客=60%
-推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
+差值分析：P主=48% P平=28% P客=24%
+推荐：主胜 信心3/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日002 大阪钢巴 vs 广岛三箭 [日职] 14:00</t>
         </is>
       </c>
     </row>
     <row r="12" ht="130" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：14:00
 联赛：日职
 竞彩SP：3.45 / 3.14 / 1.92
 让球SP(真实)：1.66/3.62/4.00
-差值分析：P主=91% P平=100% P客=164%
-推荐：客胜 信心6/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+差值分析：P主=34% P平=30% P客=36%
+推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日003 柏太阳神 vs 川崎前锋 [日职] 15:00</t>
         </is>
       </c>
     </row>
     <row r="20" ht="130" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：15:00
 联赛：日职
 竞彩SP：1.90 / 3.35 / 3.28
 让球SP(真实)：3.75/3.75/1.68
-差值分析：P主=176% P平=100% P客=102%
-推荐：主胜 信心6/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+差值分析：P主=43% P平=29% P客=28%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日004 千叶市原 vs 町田泽维 [日职] 16:00</t>
         </is>
       </c>
     </row>
     <row r="28" ht="130" customHeight="1">
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：16:00
 联赛：日职
 竞彩SP：4.00 / 3.25 / 1.75
 让球SP(真实)：1.83/3.20/3.70
-差值分析：P主=81% P平=100% P客=186%
-推荐：客胜 信心6/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+差值分析：P主=33% P平=30% P客=37%
+推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日005 维罗纳 vs 科莫 [意甲] 18:30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="130" customHeight="1">
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：意甲
 竞彩SP：8.55 / 4.70 / 1.25
 让球SP(真实)：3.18/3.32/1.95
-差值分析：P主=40% P平=73% P客=276%
-推荐：客胜 信心5/10 比分1-2(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+差值分析：P主=32% P平=27% P客=41%
+推荐：客胜 信心4/10 比分1-2(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日006 杜塞多夫 vs 埃沃斯堡 [德乙] 19:30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="130" customHeight="1">
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：19:30
 联赛：德乙
-竞彩SP：3.10 / 3.72 / 1.86
-让球SP(真实)：1.72/3.90/3.43
-差值分析：P主=116% P平=96% P客=193%
-推荐：客胜 信心6/10 比分0-1(泊松) 半全场负负 大小球小2.5(43%) 备选半全场:平负
+竞彩SP：3.06 / 3.65 / 1.89
+让球SP(真实)：1.68/3.90/3.60
+差值分析：P主=35% P平=29% P客=36%
+推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(43%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日007 马洛卡 vs 比利亚雷 [西甲] 20:00</t>
         </is>
       </c>
     </row>
     <row r="52" ht="130" customHeight="1">
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：20:00
 联赛：西甲
-竞彩SP：2.30 / 3.40 / 2.50
-让球SP(真实)：暂无
-差值分析：P主=148% P平=100% P客=136%
-推荐：不投 信心2/10 比分1-1(泊松) 半全场— 大小球小2.5(44%) 备选半全场:—
+竞彩SP：2.15 / 3.40 / 2.70
+让球SP(真实)：4.70/3.80/1.53
+差值分析：P主=41% P平=28% P客=31%
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日008 罗森博格 vs 利勒斯特 [挪超] 20:30</t>
         </is>
       </c>
     </row>
     <row r="60" ht="130" customHeight="1">
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：20:30
 联赛：挪超
-竞彩SP：2.52 / 3.45 / 2.26
-让球SP(真实)：1.49/4.05/4.75
-差值分析：P主=137% P平=100% P客=153%
-推荐：不投 信心2/10 比分1-1(泊松) 半全场— 大小球小2.5(42%) 备选半全场:—
-让球:让+1 输盘=让平/让负 </t>
+竞彩SP：2.45 / 3.45 / 2.32
+让球SP(真实)：1.47/4.10/4.90
+差值分析：P主=37% P平=30% P客=33%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日009 伯恩利 vs 维拉 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="68" ht="130" customHeight="1">
-      <c r="B68" s="17" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：5.50 / 4.20 / 1.41
-让球SP(真实)：2.42/3.40/2.37
-差值分析：P主=69% P平=90% P客=269%
-推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+竞彩SP：5.75 / 4.23 / 1.39
+让球SP(真实)：2.48/3.35/2.34
+差值分析：P主=31% P平=27% P客=41%
+推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="inlineStr">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日010 水晶宫 vs 埃弗顿 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="76" ht="130" customHeight="1">
-      <c r="B76" s="17" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
 竞彩SP：2.85 / 3.00 / 2.25
 让球SP(真实)：1.49/3.90/4.95
-差值分析：P主=95% P平=90% P客=120%
-推荐：平局 信心2/10 比分1-1(泊松) 半全场平平 大小球小2.5(52%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+差值分析：P主=37% P平=30% P客=33%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(64%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="inlineStr">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日011 诺丁汉 vs 纽卡斯尔 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="84" ht="130" customHeight="1">
-      <c r="B84" s="17" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：2.65 / 3.32 / 2.22
-让球SP(真实)：1.49/4.20/4.55
-差值分析：P主=125% P平=100% P客=150%
-推荐：客胜 信心2/10 比分1-2(泊松) 半全场负负 大小球大2.5(67%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+竞彩SP：2.70 / 3.33 / 2.18
+让球SP(真实)：1.51/4.10/4.47
+差值分析：P主=36% P平=28% P客=35%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="inlineStr">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日012 克雷莫纳 vs 比萨 [意甲] 21:00</t>
         </is>
       </c>
     </row>
     <row r="92" ht="130" customHeight="1">
-      <c r="B92" s="17" t="inlineStr">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：意甲
 竞彩SP：1.60 / 3.45 / 4.65
 让球SP(真实)：3.10/3.25/2.01
-差值分析：P主=202% P平=94% P客=70%
-推荐：主胜 信心6/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
+差值分析：P主=46% P平=28% P客=26%
+推荐：主胜 信心4/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="inlineStr">
+      <c r="A99" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日013 佛罗伦萨 vs 热那亚 [意甲] 21:00</t>
         </is>
       </c>
     </row>
     <row r="100" ht="130" customHeight="1">
-      <c r="B100" s="17" t="inlineStr">
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：意甲
 竞彩SP：1.89 / 3.00 / 3.74
 让球SP(真实)：4.10/3.40/1.69
-差值分析：P主=143% P平=90% P客=72%
-推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
+差值分析：P主=43% P平=29% P客=28%
+推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="16" t="inlineStr">
+      <c r="A107" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日014 汉堡 vs 弗赖堡 [德甲] 21:30</t>
         </is>
       </c>
     </row>
     <row r="108" ht="130" customHeight="1">
-      <c r="B108" s="17" t="inlineStr">
+      <c r="B108" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:30
 联赛：德甲
 竞彩SP：2.52 / 3.35 / 2.31
 让球SP(真实)：1.47/4.15/4.80
-差值分析：P主=133% P平=100% P客=145%
-推荐：不投 信心2/10 比分1-1(泊松) 半全场— 大小球小2.5(45%) 备选半全场:—
-让球:让+1 输盘=让平/让负 </t>
+差值分析：P主=37% P平=30% P客=33%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(57%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="16" t="inlineStr">
+      <c r="A115" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日015 毕尔巴鄂 vs 巴伦西亚 [西甲] 22:15</t>
         </is>
       </c>
     </row>
     <row r="116" ht="130" customHeight="1">
-      <c r="B116" s="17" t="inlineStr">
+      <c r="B116" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:15
 联赛：西甲
-竞彩SP：1.54 / 3.57 / 5.00
-让球SP(真实)：3.00/3.02/2.15
-差值分析：P主=224% P平=97% P客=69%
-推荐：主胜 信心5/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
+竞彩SP：1.52 / 3.58 / 5.20
+让球SP(真实)：3.00/2.93/2.20
+差值分析：P主=48% P平=27% P客=25%
+推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="16" t="inlineStr">
+      <c r="A123" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日016 费耶诺德 vs 阿尔克马 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="124" ht="130" customHeight="1">
-      <c r="B124" s="17" t="inlineStr">
+      <c r="B124" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
 竞彩SP：1.72 / 3.80 / 3.52
 让球SP(真实)：3.08/3.80/1.85
-差值分析：P主=210% P平=95% P客=102%
-推荐：主胜 信心6/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(48%) 备选半全场:平胜
+差值分析：P主=49% P平=26% P客=25%
+推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(48%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="16" t="inlineStr">
+      <c r="A131" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日017 阿贾克斯 vs 乌德勒支 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="132" ht="130" customHeight="1">
-      <c r="B132" s="17" t="inlineStr">
+      <c r="B132" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
-竞彩SP：1.43 / 4.35 / 5.00
-让球SP(真实)：2.28/3.65/2.40
-差值分析：P主=259% P平=85% P客=74%
+竞彩SP：1.41 / 4.50 / 5.05
+让球SP(真实)：2.26/3.65/2.42
+差值分析：P主=53% P平=25% P客=22%
 推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(48%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="16" t="inlineStr">
+      <c r="A139" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日018 格罗宁根 vs 奈梅亨 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="140" ht="130" customHeight="1">
-      <c r="B140" s="17" t="inlineStr">
+      <c r="B140" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
-竞彩SP：2.74 / 3.65 / 2.04
-让球SP(真实)：1.58/4.05/4.00
-差值分析：P主=130% P平=98% P客=175%
-推荐：客胜 信心2/10 比分1-2(泊松) 半全场负负 大小球大2.5(58%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+竞彩SP：2.77 / 3.70 / 2.01
+让球SP(真实)：1.60/4.00/3.93
+差值分析：P主=37% P平=28% P客=35%
+推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(58%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="16" t="inlineStr">
+      <c r="A147" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日019 西汉姆联 vs 阿森纳 [英超] 23:30</t>
         </is>
       </c>
     </row>
     <row r="148" ht="130" customHeight="1">
-      <c r="B148" s="17" t="inlineStr">
+      <c r="B148" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：23:30
 联赛：英超
-竞彩SP：5.70 / 4.26 / 1.39
-让球SP(真实)：2.51/3.45/2.27
-差值分析：P主=67% P平=89% P客=274%
-推荐：客胜 信心5/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+竞彩SP：5.80 / 4.40 / 1.37
+让球SP(真实)：2.54/3.43/2.25
+差值分析：P主=29% P平=26% P客=45%
+推荐：客胜 信心4/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="16" t="inlineStr">
+      <c r="A155" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日020 科隆 vs 海登海姆 [德甲] 23:30</t>
         </is>
       </c>
     </row>
     <row r="156" ht="130" customHeight="1">
-      <c r="B156" s="17" t="inlineStr">
+      <c r="B156" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：23:30
 联赛：德甲
 竞彩SP：1.94 / 3.70 / 2.91
 让球SP(真实)：3.55/4.15/1.65
-差值分析：P主=190% P平=100% P客=127%
-推荐：主胜 信心6/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
+差值分析：P主=43% P平=28% P客=29%
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="16" t="inlineStr">
+      <c r="A163" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日021 帕尔马 vs 罗马 [意甲] 00:00</t>
         </is>
       </c>
     </row>
     <row r="164" ht="130" customHeight="1">
-      <c r="B164" s="17" t="inlineStr">
+      <c r="B164" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：00:00
 联赛：意甲
-竞彩SP：6.42 / 4.10 / 1.37
-让球SP(真实)：2.55/3.25/2.33
-差值分析：P主=52% P平=82% P客=246%
-推荐：客胜 信心5/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:胜负
+竞彩SP：6.65 / 4.20 / 1.35
+让球SP(真实)：2.61/3.15/2.33
+差值分析：P主=32% P平=27% P客=41%
+推荐：客胜 信心4/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:胜负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="16" t="inlineStr">
+      <c r="A171" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日022 奥维耶多 vs 赫塔费 [西甲] 00:30</t>
         </is>
       </c>
     </row>
     <row r="172" ht="130" customHeight="1">
-      <c r="B172" s="17" t="inlineStr">
+      <c r="B172" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：00:30
 联赛：西甲
 竞彩SP：2.79 / 2.70 / 2.50
 让球SP(真实)：1.39/3.80/6.80
-差值分析：P主=76% P平=79% P客=85%
-推荐：平局 信心2/10 比分1-1(泊松) 半全场平平 大小球小2.5(43%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+差值分析：P主=39% P平=30% P客=31%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="16" t="inlineStr">
+      <c r="A179" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日023 美因茨 vs 柏林联合 [德甲] 01:30</t>
         </is>
       </c>
     </row>
     <row r="180" ht="130" customHeight="1">
-      <c r="B180" s="17" t="inlineStr">
+      <c r="B180" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：01:30
 联赛：德甲
-竞彩SP：1.58 / 3.80 / 4.28
-让球SP(真实)：2.80/3.51/2.05
-差值分析：P主=235% P平=98% P客=87%
-推荐：主胜 信心5/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
+竞彩SP：1.55 / 3.80 / 4.55
+让球SP(真实)：2.75/3.40/2.12
+差值分析：P主=44% P平=27% P客=29%
+推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="16" t="inlineStr">
+      <c r="A187" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日024 吉达联合 vs 达马克 [沙职] 02:00</t>
         </is>
       </c>
     </row>
     <row r="188" ht="130" customHeight="1">
-      <c r="B188" s="17" t="inlineStr">
+      <c r="B188" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙职
 竞彩SP：1.32 / 4.50 / 6.70
 让球SP(真实)：2.08/3.43/2.80
-差值分析：P主=337% P平=99% P客=66%
-推荐：主胜 信心7/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
+差值分析：P主=50% P平=26% P客=24%
+推荐：主胜 信心1/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="16" t="inlineStr">
+      <c r="A195" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日025 AC米兰 vs 亚特兰大 [意甲] 02:45</t>
         </is>
       </c>
     </row>
     <row r="196" ht="130" customHeight="1">
-      <c r="B196" s="17" t="inlineStr">
+      <c r="B196" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：02:45
 联赛：意甲
-竞彩SP：1.94 / 3.22 / 3.30
-让球SP(真实)：4.08/3.60/1.65
-差值分析：P主=164% P平=99% P客=96%
-推荐：主胜 信心6/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:负胜
+竞彩SP：1.94 / 3.15 / 3.37
+让球SP(真实)：4.15/3.54/1.65
+差值分析：P主=41% P平=27% P客=31%
+推荐：主胜 信心4/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:负胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="16" t="inlineStr">
+      <c r="A203" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日026 巴萨 vs 皇马 [西甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="204" ht="130" customHeight="1">
-      <c r="B204" s="17" t="inlineStr">
+      <c r="B204" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：西甲
 竞彩SP：1.51 / 4.65 / 3.96
 让球SP(真实)：2.40/3.85/2.21
-差值分析：P主=241% P平=78% P客=92%
-推荐：主胜 信心6/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+差值分析：P主=43% P平=25% P客=32%
+推荐：主胜 信心3/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="16" t="inlineStr">
+      <c r="A211" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日027 欧塞尔 vs 尼斯 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="212" ht="130" customHeight="1">
-      <c r="B212" s="17" t="inlineStr">
+      <c r="B212" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：法甲
-竞彩SP：2.23 / 3.15 / 2.75
+竞彩SP：2.25 / 3.05 / 2.80
 让球SP(真实)：5.00/3.88/1.49
-差值分析：P主=141% P平=100% P客=115%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+差值分析：P主=40% P平=30% P客=30%
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="16" t="inlineStr">
+      <c r="A219" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日028 巴黎圣曼 vs 布雷斯特 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="220" ht="130" customHeight="1">
-      <c r="B220" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：03:00
+      <c r="B220" s="14" t="inlineStr">
+        <is>
+          <t>时间：03:00
 联赛：法甲
 竞彩SP：0.00 / 0.00 / 0.00
 让球SP(真实)：暂无
-差值分析：P主=0% P平=0% P客=0%
-推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
-让球:让-2 —=— </t>
+差值分析：P主=38% P平=31% P客=31%
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+让球:让-2 输盘=让平/让负 让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="16" t="inlineStr">
+      <c r="A227" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日029 摩纳哥 vs 里尔 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="228" ht="130" customHeight="1">
-      <c r="B228" s="17" t="inlineStr">
+      <c r="B228" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：法甲
 竞彩SP：2.23 / 3.45 / 2.56
 让球SP(真实)：4.70/4.08/1.49
-差值分析：P主=155% P平=100% P客=135%
-推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:负胜
+差值分析：P主=40% P平=27% P客=33%
+推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:负胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="16" t="inlineStr">
+      <c r="A235" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日030 纽约城 vs 哥伦布 [美职] 04:30</t>
         </is>
       </c>
     </row>
     <row r="236" ht="130" customHeight="1">
-      <c r="B236" s="17" t="inlineStr">
+      <c r="B236" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：04:30
 联赛：美职
 竞彩SP：2.25 / 3.35 / 2.59
 让球SP(真实)：4.75/3.97/1.50
-差值分析：P主=149% P平=100% P客=129%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+差值分析：P主=41% P平=29% P客=30%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -7005,7 +6793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7019,7 +6807,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>🔗 串关方案（2串1/3串1/4串1/5串1/6串1）</t>
         </is>
@@ -7068,7 +6856,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>A. 胜平负串关</t>
         </is>
@@ -7082,13 +6870,13 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日003</t>
+          <t>周日016+周日017</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)</t>
+          <t>·费耶诺德:主胜(1.72)
+·阿贾克斯:主胜(1.41)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -7101,171 +6889,17 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>7.30元</t>
+          <t>4.86元</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>3.65倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)
-·千叶市原:客胜(1.75)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2注×2元</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>12.76元</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>6.38倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>4串1</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)
-·千叶市原:客胜(1.75)
-·杜塞多夫:客胜(1.86)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>2注×2元</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>23.74元</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>11.87倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006+周日012</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)
-·千叶市原:客胜(1.75)
-·杜塞多夫:客胜(1.86)
-·克雷莫纳:主胜(1.60)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2注×2元</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>38.00元</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>19.00倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006+周日012+周日016</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)
-·柏太阳神:主胜(1.90)
-·千叶市原:客胜(1.75)
-·杜塞多夫:客胜(1.86)
-·克雷莫纳:主胜(1.60)
-·费耶诺德:主胜(1.72)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>2注×2元</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>65.36元</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>32.68倍</t>
+          <t>2.43倍</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>B. 比分串关（泊松模型独立计算）</t>
         </is>
@@ -7284,13 +6918,13 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日003</t>
+          <t>周日016+周日017</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:0-1(9.6)
-·柏太阳神:1-0(9.5)</t>
+          <t>·费耶诺德:2-0(8.6)
+·阿贾克斯:2-0(7.0)</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
@@ -7298,7 +6932,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -7308,164 +6942,23 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>约182元</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>比分</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:0-1(9.6)
-·柏太阳神:1-0(9.5)
-·千叶市原:0-1(8.8)</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>约1596元</t>
+          <t>约121元</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>C. 混合串关（胜平负+让球穿盘）</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="20" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)/让平/让负
-·柏太阳神:主胜(1.90)/让平/让负
-·千叶市原:客胜(1.75)/让平/让负</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>6.38</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>12.77元</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>4串1</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:客胜(1.92)/让平/让负
-·柏太阳神:主胜(1.90)/让平/让负
-·千叶市原:客胜(1.75)/让平/让负
-·杜塞多夫:客胜(1.86)/让平/让负</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>11.87</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>23.75元</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>D. 半全场串关（从泊松比分推半全场）</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="20" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7480,13 +6973,13 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>周日002+周日003</t>
+          <t>周日016+周日017</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>·大阪钢巴:负负(2.5)
-·柏太阳神:胜胜(2.2)</t>
+          <t>·费耶诺德:胜胜(2.2)
+·阿贾克斯:胜胜(2.2)</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
@@ -7494,7 +6987,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -7504,181 +6997,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>11.00元</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:负负(2.5)
-·柏太阳神:胜胜(2.2)
-·千叶市原:负负(2.5)</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>13.75</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>27.50元</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>4串1</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:负负(2.5)
-·柏太阳神:胜胜(2.2)
-·千叶市原:负负(2.5)
-·杜塞多夫:负负(2.5)</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>34.38</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>68.75元</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006+周日012</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:负负(2.5)
-·柏太阳神:胜胜(2.2)
-·千叶市原:负负(2.5)
-·杜塞多夫:负负(2.5)
-·克雷莫纳:胜胜(2.2)</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>75.62</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>151.25元</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>周日002+周日003+周日004+周日006+周日012+周日016</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>·大阪钢巴:负负(2.5)
-·柏太阳神:胜胜(2.2)
-·千叶市原:负负(2.5)
-·杜塞多夫:负负(2.5)
-·克雷莫纳:胜胜(2.2)
-·费耶诺德:胜胜(2.2)</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>166.38</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>332.75元</t>
+          <t>9.68元</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-10.xlsx
+++ b/Aii竞彩推荐_2026-05-10.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -148,7 +148,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -519,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J159"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -544,7 +543,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 19:10</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 19:29</t>
         </is>
       </c>
     </row>
@@ -894,7 +893,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP3.06/3.65/1.89 让球+1</t>
+          <t>SP3.05/3.56/1.92 让球+1</t>
         </is>
       </c>
     </row>
@@ -988,7 +987,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP2.45/3.45/2.32 让球+1</t>
+          <t>SP2.38/3.45/2.39 让球+1</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1222,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>SP1.89/3.00/3.74 让球-1</t>
+          <t>SP1.85/2.95/4.00 让球-1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1457,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>SP2.77/3.70/2.01 让球+1</t>
+          <t>SP2.74/3.65/2.04 让球+1</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1833,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>SP1.51/4.65/3.96 让球-1</t>
+          <t>SP1.51/4.50/4.08 让球-1</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2028,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 19:10）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 19:29）</t>
         </is>
       </c>
     </row>
@@ -2332,13 +2331,13 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -2347,7 +2346,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2357,7 +2356,7 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
@@ -2424,13 +2423,13 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>3.45</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -2439,17 +2438,17 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -2654,13 +2653,13 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -2669,17 +2668,17 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -2884,13 +2883,13 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2899,17 +2898,17 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
           <t>4.00</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>3.93</t>
         </is>
       </c>
     </row>
@@ -3255,10 +3254,10 @@
         <v>1.51</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -3572,7 +3571,7 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=48%P平=28%P客=24%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=47%P平=28%P客=25%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3675,7 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=29%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=44%P平=29%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3727,7 @@
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=33%P平=30%P客=37%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=32%P平=30%P客=37%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3796,7 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -3807,22 +3806,22 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -3832,7 +3831,7 @@
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=29%P客=36%|泊松比分0-1|半全场平负|大小球小2.5(43%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=36%P平=29%P客=35%|泊松比分1-0|半全场平负|大小球小2.5(43%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3905,7 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -3936,7 +3935,7 @@
       </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=37%P平=30%P客=33%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球+1=走水/让平</t>
+          <t>贝叶斯P主=40%P平=29%P客=31%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3987,7 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=27%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=32%P平=28%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4195,7 @@
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=29%P客=28%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=44%P平=29%P客=28%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4403,7 @@
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=53%P平=25%P客=22%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=52%P平=25%P客=23%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4455,7 @@
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=37%P平=28%P客=35%|泊松比分2-1|半全场平负|大小球大2.5(58%)|让球+1=走水/让平</t>
+          <t>贝叶斯P主=37%P平=29%P客=34%|泊松比分2-1|半全场平负|大小球大2.5(58%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4559,7 @@
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=25%P客=32%|泊松比分3-2|半全场负负|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=44%P平=25%P客=32%|泊松比分3-2|半全场负负|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5087,1041 +5086,217 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>🏆 14场胜负彩+任选9方案</t>
+          <t>🏆 14场胜负彩+任选9（暂无官方数据）</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>场次</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>联赛</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>主队</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>客队</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>信心</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>胆材</t>
-        </is>
-      </c>
-      <c r="J114" s="5" t="inlineStr">
-        <is>
-          <t>让球提示</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B115" s="10" t="inlineStr">
-        <is>
-          <t>周日016</t>
-        </is>
-      </c>
-      <c r="C115" s="10" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D115" s="10" t="inlineStr">
-        <is>
-          <t>费耶诺德</t>
-        </is>
-      </c>
-      <c r="E115" s="10" t="inlineStr">
-        <is>
-          <t>阿尔克马</t>
-        </is>
-      </c>
-      <c r="F115" s="10" t="inlineStr">
-        <is>
-          <t>1.72/3.80/3.52</t>
-        </is>
-      </c>
-      <c r="G115" s="10" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H115" s="10" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I115" s="10" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J115" s="10" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t>周日017</t>
-        </is>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D116" s="10" t="inlineStr">
-        <is>
-          <t>阿贾克斯</t>
-        </is>
-      </c>
-      <c r="E116" s="10" t="inlineStr">
-        <is>
-          <t>乌德勒支</t>
-        </is>
-      </c>
-      <c r="F116" s="10" t="inlineStr">
-        <is>
-          <t>1.41/4.50/5.05</t>
-        </is>
-      </c>
-      <c r="G116" s="10" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="I116" s="10" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J116" s="10" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>周日005</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>维罗纳</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>科莫</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>8.55/4.70/1.25</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J117" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>周日006</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>德乙</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>杜塞多夫</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>埃沃斯堡</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>3.06/3.65/1.89</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J118" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>周日007</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>马洛卡</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>比利亚雷</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>2.15/3.40/2.70</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J119" s="6" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>周日009</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>伯恩利</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>维拉</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>5.75/4.23/1.39</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J120" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t>周日012</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t>克雷莫纳</t>
-        </is>
-      </c>
-      <c r="E121" s="10" t="inlineStr">
-        <is>
-          <t>比萨</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr">
-        <is>
-          <t>1.60/3.45/4.65</t>
-        </is>
-      </c>
-      <c r="G121" s="10" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H121" s="10" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I121" s="10" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J121" s="10" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>周日013</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>佛罗伦萨</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>热那亚</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>1.89/3.00/3.74</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J122" s="6" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t>周日015</t>
-        </is>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D123" s="10" t="inlineStr">
-        <is>
-          <t>毕尔巴鄂</t>
-        </is>
-      </c>
-      <c r="E123" s="10" t="inlineStr">
-        <is>
-          <t>巴伦西亚</t>
-        </is>
-      </c>
-      <c r="F123" s="10" t="inlineStr">
-        <is>
-          <t>1.52/3.58/5.20</t>
-        </is>
-      </c>
-      <c r="G123" s="10" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H123" s="10" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I123" s="10" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J123" s="10" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>周日018</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>格罗宁根</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>奈梅亨</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>2.77/3.70/2.01</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J124" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B125" s="10" t="inlineStr">
-        <is>
-          <t>周日019</t>
-        </is>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="D125" s="10" t="inlineStr">
-        <is>
-          <t>西汉姆联</t>
-        </is>
-      </c>
-      <c r="E125" s="10" t="inlineStr">
-        <is>
-          <t>阿森纳</t>
-        </is>
-      </c>
-      <c r="F125" s="10" t="inlineStr">
-        <is>
-          <t>5.80/4.40/1.37</t>
-        </is>
-      </c>
-      <c r="G125" s="10" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H125" s="10" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I125" s="10" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J125" s="10" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>周日020</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>德甲</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>科隆</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>海登海姆</t>
-        </is>
-      </c>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>1.94/3.70/2.91</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="6" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>周日021</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>帕尔马</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>6.65/4.20/1.35</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J127" s="6" t="inlineStr">
-        <is>
-          <t>让+1盘</t>
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>🔴 铁律：无官方来源不编数据。请查lottery.gov.cn或sporttery.cn传统足彩页面获取当期14场列表</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B128" s="10" t="inlineStr">
-        <is>
-          <t>周日023</t>
-        </is>
-      </c>
-      <c r="C128" s="10" t="inlineStr">
-        <is>
-          <t>德甲</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
-        <is>
-          <t>美因茨</t>
-        </is>
-      </c>
-      <c r="E128" s="10" t="inlineStr">
-        <is>
-          <t>柏林联合</t>
-        </is>
-      </c>
-      <c r="F128" s="10" t="inlineStr">
-        <is>
-          <t>1.55/3.80/4.55</t>
-        </is>
-      </c>
-      <c r="G128" s="10" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H128" s="10" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
-      </c>
-      <c r="I128" s="10" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J128" s="10" t="inlineStr">
-        <is>
-          <t>让-1盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>📋 任选9方案（4胆+5双=32注=64元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日016 费耶诺德vs阿尔克马 → 主胜 (信心5/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日017 阿贾克斯vs乌德勒支 → 主胜 (信心5/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日005 维罗纳vs科莫 → 客胜/平局 (信心4/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日006 杜塞多夫vs埃沃斯堡 → 客胜/平局 (信心4/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日007 马洛卡vs比利亚雷 → 主胜/平局 (信心4/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日009 伯恩利vs维拉 → 客胜/平局 (信心4/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日012 克雷莫纳vs比萨 → 主胜 (信心4/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日013 佛罗伦萨vs热那亚 → 主胜/平局 (信心4/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="11" t="inlineStr">
-        <is>
-          <t>⬜ 周日015 毕尔巴鄂vs巴伦西亚 → 主胜 (信心4/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>方案</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>场次组合</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>每场选择</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>注数</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
+      <c r="E128" s="5" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr">
         <is>
           <t>综合SP</t>
         </is>
       </c>
-      <c r="G149" s="5" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="6" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>2串1</t>
         </is>
       </c>
-      <c r="B150" s="6" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>周日016+周日017</t>
         </is>
       </c>
-      <c r="C150" s="9" t="inlineStr">
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>·费耶诺德:主胜(1.72)
 ·阿贾克斯:主胜(1.41)</t>
         </is>
       </c>
-      <c r="D150" s="6" t="n">
+      <c r="D129" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E129" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F150" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <t>2.43</t>
         </is>
       </c>
-      <c r="G150" s="6" t="inlineStr">
+      <c r="G129" s="6" t="inlineStr">
         <is>
           <t>1.72×1.41=2.43</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>⚠️ 核心信号</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>信号</t>
         </is>
       </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>场次</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>解读</t>
         </is>
       </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>应对</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="10" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>🟢 高信心(7/10+)</t>
         </is>
       </c>
-      <c r="B156" s="6" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>015/017/023/024/029</t>
         </is>
       </c>
-      <c r="C156" s="6" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
         <is>
           <t>5场贝叶斯概率最高，SP均&lt;1.45</t>
         </is>
       </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="D135" s="6" t="inlineStr">
         <is>
           <t>作胆材/串关核心</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="10" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>🟢 让球SP真实数据</t>
         </is>
       </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C157" s="6" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>从500.com让球页提取，非估算</t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>可用作让球分析</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="8" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
       </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>004/007/011</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>平局概率30-35%，接近主胜</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>双选或慎入</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="8" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
       </c>
-      <c r="B159" s="6" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="10">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A135:J135"/>
-    <mergeCell ref="A131:J131"/>
-    <mergeCell ref="A140:J140"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A114:J114"/>
     <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A134:J134"/>
-    <mergeCell ref="A138:J138"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A132:J132"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A137:J137"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A136:J136"/>
-    <mergeCell ref="A139:J139"/>
-    <mergeCell ref="A154:J154"/>
     <mergeCell ref="A113:J113"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
@@ -6143,41 +5318,41 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>📋 2026-05-10 每场完整分析（30场）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日001 蔚山现代 vs 富川FC [韩职] 13:00</t>
         </is>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1">
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：13:00
 联赛：韩职
 竞彩SP：1.51 / 3.55 / 5.40
 让球SP(真实)：2.86/3.12/2.18
-差值分析：P主=48% P平=28% P客=24%
+差值分析：P主=47% P平=28% P客=25%
 推荐：主胜 信心3/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日002 大阪钢巴 vs 广岛三箭 [日职] 14:00</t>
         </is>
       </c>
     </row>
     <row r="12" ht="130" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：14:00
 联赛：日职
@@ -6190,54 +5365,54 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日003 柏太阳神 vs 川崎前锋 [日职] 15:00</t>
         </is>
       </c>
     </row>
     <row r="20" ht="130" customHeight="1">
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：15:00
 联赛：日职
 竞彩SP：1.90 / 3.35 / 3.28
 让球SP(真实)：3.75/3.75/1.68
-差值分析：P主=43% P平=29% P客=28%
+差值分析：P主=44% P平=29% P客=28%
 推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日004 千叶市原 vs 町田泽维 [日职] 16:00</t>
         </is>
       </c>
     </row>
     <row r="28" ht="130" customHeight="1">
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：16:00
 联赛：日职
 竞彩SP：4.00 / 3.25 / 1.75
 让球SP(真实)：1.83/3.20/3.70
-差值分析：P主=33% P平=30% P客=37%
+差值分析：P主=32% P平=30% P客=37%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日005 维罗纳 vs 科莫 [意甲] 18:30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="130" customHeight="1">
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：意甲
@@ -6250,34 +5425,34 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日006 杜塞多夫 vs 埃沃斯堡 [德乙] 19:30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="130" customHeight="1">
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：19:30
 联赛：德乙
-竞彩SP：3.06 / 3.65 / 1.89
-让球SP(真实)：1.68/3.90/3.60
-差值分析：P主=35% P平=29% P客=36%
-推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(43%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+竞彩SP：3.05 / 3.56 / 1.92
+让球SP(真实)：1.66/3.90/3.70
+差值分析：P主=36% P平=29% P客=35%
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日007 马洛卡 vs 比利亚雷 [西甲] 20:00</t>
         </is>
       </c>
     </row>
     <row r="52" ht="130" customHeight="1">
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：20:00
 联赛：西甲
@@ -6290,54 +5465,54 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日008 罗森博格 vs 利勒斯特 [挪超] 20:30</t>
         </is>
       </c>
     </row>
     <row r="60" ht="130" customHeight="1">
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：20:30
 联赛：挪超
-竞彩SP：2.45 / 3.45 / 2.32
-让球SP(真实)：1.47/4.10/4.90
-差值分析：P主=37% P平=30% P客=33%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+竞彩SP：2.38 / 3.45 / 2.39
+让球SP(真实)：1.44/4.25/5.00
+差值分析：P主=40% P平=29% P客=31%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日009 伯恩利 vs 维拉 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="68" ht="130" customHeight="1">
-      <c r="B68" s="14" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
 竞彩SP：5.75 / 4.23 / 1.39
 让球SP(真实)：2.48/3.35/2.34
-差值分析：P主=31% P平=27% P客=41%
+差值分析：P主=32% P平=28% P客=40%
 推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日010 水晶宫 vs 埃弗顿 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="76" ht="130" customHeight="1">
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
@@ -6350,14 +5525,14 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="13" t="inlineStr">
+      <c r="A83" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日011 诺丁汉 vs 纽卡斯尔 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="84" ht="130" customHeight="1">
-      <c r="B84" s="14" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
@@ -6370,14 +5545,14 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="13" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日012 克雷莫纳 vs 比萨 [意甲] 21:00</t>
         </is>
       </c>
     </row>
     <row r="92" ht="130" customHeight="1">
-      <c r="B92" s="14" t="inlineStr">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：意甲
@@ -6390,34 +5565,34 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="13" t="inlineStr">
+      <c r="A99" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日013 佛罗伦萨 vs 热那亚 [意甲] 21:00</t>
         </is>
       </c>
     </row>
     <row r="100" ht="130" customHeight="1">
-      <c r="B100" s="14" t="inlineStr">
+      <c r="B100" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：意甲
-竞彩SP：1.89 / 3.00 / 3.74
-让球SP(真实)：4.10/3.40/1.69
-差值分析：P主=43% P平=29% P客=28%
+竞彩SP：1.85 / 2.95 / 4.00
+让球SP(真实)：4.00/3.30/1.74
+差值分析：P主=44% P平=29% P客=28%
 推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="13" t="inlineStr">
+      <c r="A107" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日014 汉堡 vs 弗赖堡 [德甲] 21:30</t>
         </is>
       </c>
     </row>
     <row r="108" ht="130" customHeight="1">
-      <c r="B108" s="14" t="inlineStr">
+      <c r="B108" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:30
 联赛：德甲
@@ -6430,14 +5605,14 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="13" t="inlineStr">
+      <c r="A115" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日015 毕尔巴鄂 vs 巴伦西亚 [西甲] 22:15</t>
         </is>
       </c>
     </row>
     <row r="116" ht="130" customHeight="1">
-      <c r="B116" s="14" t="inlineStr">
+      <c r="B116" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:15
 联赛：西甲
@@ -6450,14 +5625,14 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="13" t="inlineStr">
+      <c r="A123" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日016 费耶诺德 vs 阿尔克马 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="124" ht="130" customHeight="1">
-      <c r="B124" s="14" t="inlineStr">
+      <c r="B124" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
@@ -6470,54 +5645,54 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="13" t="inlineStr">
+      <c r="A131" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日017 阿贾克斯 vs 乌德勒支 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="132" ht="130" customHeight="1">
-      <c r="B132" s="14" t="inlineStr">
+      <c r="B132" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
 竞彩SP：1.41 / 4.50 / 5.05
 让球SP(真实)：2.26/3.65/2.42
-差值分析：P主=53% P平=25% P客=22%
+差值分析：P主=52% P平=25% P客=23%
 推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(48%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="13" t="inlineStr">
+      <c r="A139" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日018 格罗宁根 vs 奈梅亨 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="140" ht="130" customHeight="1">
-      <c r="B140" s="14" t="inlineStr">
+      <c r="B140" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
-竞彩SP：2.77 / 3.70 / 2.01
-让球SP(真实)：1.60/4.00/3.93
-差值分析：P主=37% P平=28% P客=35%
+竞彩SP：2.74 / 3.65 / 2.04
+让球SP(真实)：1.58/4.05/4.00
+差值分析：P主=37% P平=29% P客=34%
 推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(58%) 备选半全场:平胜
 让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="13" t="inlineStr">
+      <c r="A147" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日019 西汉姆联 vs 阿森纳 [英超] 23:30</t>
         </is>
       </c>
     </row>
     <row r="148" ht="130" customHeight="1">
-      <c r="B148" s="14" t="inlineStr">
+      <c r="B148" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：23:30
 联赛：英超
@@ -6530,34 +5705,34 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="13" t="inlineStr">
+      <c r="A155" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日020 科隆 vs 海登海姆 [德甲] 23:30</t>
         </is>
       </c>
     </row>
     <row r="156" ht="130" customHeight="1">
-      <c r="B156" s="14" t="inlineStr">
+      <c r="B156" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：23:30
 联赛：德甲
 竞彩SP：1.94 / 3.70 / 2.91
 让球SP(真实)：3.55/4.15/1.65
-差值分析：P主=43% P平=28% P客=29%
+差值分析：P主=44% P平=27% P客=29%
 推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="13" t="inlineStr">
+      <c r="A163" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日021 帕尔马 vs 罗马 [意甲] 00:00</t>
         </is>
       </c>
     </row>
     <row r="164" ht="130" customHeight="1">
-      <c r="B164" s="14" t="inlineStr">
+      <c r="B164" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：00:00
 联赛：意甲
@@ -6570,14 +5745,14 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="13" t="inlineStr">
+      <c r="A171" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日022 奥维耶多 vs 赫塔费 [西甲] 00:30</t>
         </is>
       </c>
     </row>
     <row r="172" ht="130" customHeight="1">
-      <c r="B172" s="14" t="inlineStr">
+      <c r="B172" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：00:30
 联赛：西甲
@@ -6590,14 +5765,14 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="13" t="inlineStr">
+      <c r="A179" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日023 美因茨 vs 柏林联合 [德甲] 01:30</t>
         </is>
       </c>
     </row>
     <row r="180" ht="130" customHeight="1">
-      <c r="B180" s="14" t="inlineStr">
+      <c r="B180" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：01:30
 联赛：德甲
@@ -6610,14 +5785,14 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="13" t="inlineStr">
+      <c r="A187" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日024 吉达联合 vs 达马克 [沙职] 02:00</t>
         </is>
       </c>
     </row>
     <row r="188" ht="130" customHeight="1">
-      <c r="B188" s="14" t="inlineStr">
+      <c r="B188" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙职
@@ -6630,14 +5805,14 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="13" t="inlineStr">
+      <c r="A195" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日025 AC米兰 vs 亚特兰大 [意甲] 02:45</t>
         </is>
       </c>
     </row>
     <row r="196" ht="130" customHeight="1">
-      <c r="B196" s="14" t="inlineStr">
+      <c r="B196" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：02:45
 联赛：意甲
@@ -6650,34 +5825,34 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="13" t="inlineStr">
+      <c r="A203" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日026 巴萨 vs 皇马 [西甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="204" ht="130" customHeight="1">
-      <c r="B204" s="14" t="inlineStr">
+      <c r="B204" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：西甲
-竞彩SP：1.51 / 4.65 / 3.96
+竞彩SP：1.51 / 4.50 / 4.08
 让球SP(真实)：2.40/3.85/2.21
-差值分析：P主=43% P平=25% P客=32%
+差值分析：P主=44% P平=25% P客=32%
 推荐：主胜 信心3/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="13" t="inlineStr">
+      <c r="A211" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日027 欧塞尔 vs 尼斯 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="212" ht="130" customHeight="1">
-      <c r="B212" s="14" t="inlineStr">
+      <c r="B212" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：法甲
@@ -6690,14 +5865,14 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="13" t="inlineStr">
+      <c r="A219" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日028 巴黎圣曼 vs 布雷斯特 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="220" ht="130" customHeight="1">
-      <c r="B220" s="14" t="inlineStr">
+      <c r="B220" s="13" t="inlineStr">
         <is>
           <t>时间：03:00
 联赛：法甲
@@ -6710,14 +5885,14 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="13" t="inlineStr">
+      <c r="A227" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日029 摩纳哥 vs 里尔 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="228" ht="130" customHeight="1">
-      <c r="B228" s="14" t="inlineStr">
+      <c r="B228" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：法甲
@@ -6730,14 +5905,14 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="13" t="inlineStr">
+      <c r="A235" s="12" t="inlineStr">
         <is>
           <t>⚽ 周日030 纽约城 vs 哥伦布 [美职] 04:30</t>
         </is>
       </c>
     </row>
     <row r="236" ht="130" customHeight="1">
-      <c r="B236" s="14" t="inlineStr">
+      <c r="B236" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：04:30
 联赛：美职
@@ -6807,7 +5982,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>🔗 串关方案（2串1/3串1/4串1/5串1/6串1）</t>
         </is>
@@ -6856,7 +6031,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>A. 胜平负串关</t>
         </is>
@@ -6899,7 +6074,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>B. 比分串关（泊松模型独立计算）</t>
         </is>
@@ -6947,14 +6122,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>C. 混合串关（胜平负+让球穿盘）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>D. 半全场串关（从泊松比分推半全场）</t>
         </is>

--- a/Aii竞彩推荐_2026-05-10.xlsx
+++ b/Aii竞彩推荐_2026-05-10.xlsx
@@ -536,14 +536,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🌍 2026-05-10 周日30场竞彩推荐（今天无14场奖期）</t>
+          <t>🌍 2026-05-10 周日30场竞彩推荐+14场胜负彩(查lottery.gov.cn期号)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 19:29</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 19:37</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2025-26赛季末段，保级+欧战争夺激烈。30场竞彩。</t>
+          <t>2025-26赛季末段，保级+欧战争夺激烈。30场竞彩+14场(需查lottery.gov.cn官方奖期)。</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>SP2.85/3.00/2.25 让球+1</t>
+          <t>SP2.95/2.90/2.25 让球+1</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>SP1.94/3.70/2.91 让球-1</t>
+          <t>SP1.98/3.70/2.82 让球-1</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>SP1.51/4.50/4.08 让球-1</t>
+          <t>SP1.51/4.40/4.16 让球-1</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 19:29）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 19:37）</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F54" s="7" t="n">
         <v>2.25</v>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>3.7</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
@@ -3254,10 +3254,10 @@
         <v>1.51</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=37%P平=30%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(64%)|让球+1=走水/让平</t>
+          <t>贝叶斯P主=36%P平=30%P客=33%|泊松比分2-1|半全场平胜|大小球大2.5(64%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -5086,14 +5086,385 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>🏆 14场胜负彩+任选9（暂无官方数据）</t>
+          <t>🏆 14场胜负彩+任选9（第26074期 停售2026-05-10 20:30）</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>🔴 铁律：无官方来源不编数据。请查lottery.gov.cn或sporttery.cn传统足彩页面获取当期14场列表</t>
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>联赛</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>主队</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>客队</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>比赛日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>伯恩利</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>阿斯顿维拉</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>水晶宫</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>埃弗顿</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>诺丁汉森林</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>纽卡斯尔联</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>西汉姆联</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>阿森纳</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>汉堡</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>弗赖堡</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>科隆</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>海登海姆</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>美因茨</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>柏林联合</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>克雷莫纳</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>比萨</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>佛罗伦萨</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>热那亚</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>帕尔马</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>AC米兰</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>亚特兰大</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>毕尔巴鄂竞技</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>巴伦西亚</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>皇家奥维耶多</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>赫塔费</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5288,14 +5659,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A133:J133"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A114:J114"/>
     <mergeCell ref="A43:J43"/>
     <mergeCell ref="A113:J113"/>
     <mergeCell ref="A2:J2"/>
@@ -5516,9 +5886,9 @@
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：2.85 / 3.00 / 2.25
-让球SP(真实)：1.49/3.90/4.95
-差值分析：P主=37% P平=30% P客=33%
+竞彩SP：2.95 / 2.90 / 2.25
+让球SP(真实)：1.50/3.85/4.95
+差值分析：P主=36% P平=30% P客=33%
 推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(64%) 备选半全场:平胜
 让球:让+1 走水=让平 </t>
         </is>
@@ -5716,8 +6086,8 @@
         <is>
           <t xml:space="preserve">时间：23:30
 联赛：德甲
-竞彩SP：1.94 / 3.70 / 2.91
-让球SP(真实)：3.55/4.15/1.65
+竞彩SP：1.98 / 3.70 / 2.82
+让球SP(真实)：3.70/4.15/1.62
 差值分析：P主=44% P平=27% P客=29%
 推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
@@ -5836,7 +6206,7 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：西甲
-竞彩SP：1.51 / 4.50 / 4.08
+竞彩SP：1.51 / 4.40 / 4.16
 让球SP(真实)：2.40/3.85/2.21
 差值分析：P主=44% P平=25% P客=32%
 推荐：主胜 信心3/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜

--- a/Aii竞彩推荐_2026-05-10.xlsx
+++ b/Aii竞彩推荐_2026-05-10.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -148,6 +148,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -518,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,7 +544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 19:37</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 20:26</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1035,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP5.75/4.23/1.39 让球+1</t>
+          <t>SP5.95/4.65/1.34 让球+1</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1082,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>SP2.95/2.90/2.25 让球+1</t>
+          <t>SP2.72/2.80/2.48 让球+1</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1129,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>SP2.70/3.33/2.18 让球+1</t>
+          <t>SP2.88/3.35/2.07 让球+1</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1176,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>SP1.60/3.45/4.65 让球-1</t>
+          <t>SP1.61/3.40/4.66 让球-1</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1223,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>SP1.85/2.95/4.00 让球-1</t>
+          <t>SP1.83/2.95/4.10 让球-1</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1270,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>SP2.52/3.35/2.31 让球+1</t>
+          <t>SP2.57/3.25/2.31 让球+1</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1599,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>SP6.65/4.20/1.35 让球+1</t>
+          <t>SP6.90/4.30/1.33 让球+1</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1740,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>SP1.32/4.50/6.70 让球-1</t>
+          <t>SP1.35/4.50/6.00 让球-1</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1881,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>SP2.25/3.05/2.80 让球-1</t>
+          <t>SP2.26/2.98/2.85 让球-1</t>
         </is>
       </c>
     </row>
@@ -2021,14 +2022,14 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>SP2.25/3.35/2.59 让球-1</t>
+          <t>SP2.25/3.25/2.65 让球-1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 19:37）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 20:26）</t>
         </is>
       </c>
     </row>
@@ -2469,13 +2470,13 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -2484,17 +2485,17 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
@@ -2515,13 +2516,13 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -2530,17 +2531,17 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.60</t>
         </is>
       </c>
     </row>
@@ -2561,13 +2562,13 @@
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -2576,17 +2577,17 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.15</t>
         </is>
       </c>
     </row>
@@ -2607,13 +2608,13 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2622,17 +2623,17 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -2653,13 +2654,13 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="E57" s="6" t="n">
         <v>2.95</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -2668,17 +2669,17 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
     </row>
@@ -2699,10 +2700,10 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="F58" s="7" t="n">
         <v>2.31</v>
@@ -3021,13 +3022,13 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -3036,17 +3037,17 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
@@ -3159,13 +3160,13 @@
         </is>
       </c>
       <c r="D68" s="7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>4.5</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -3174,7 +3175,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -3184,7 +3185,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
@@ -3297,13 +3298,13 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
@@ -3312,7 +3313,7 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -3322,7 +3323,7 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
@@ -3438,10 +3439,10 @@
         <v>2.25</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -3987,7 +3988,7 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=32%P平=28%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=32%P平=27%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4040,7 @@
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=30%P客=33%|泊松比分2-1|半全场平胜|大小球大2.5(64%)|让球+1=走水/让平</t>
+          <t>贝叶斯P主=37%P平=30%P客=32%|泊松比分2-1|半全场胜胜|大小球大2.5(64%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4092,7 @@
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=28%P客=35%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球+1=走水/让平</t>
+          <t>贝叶斯P主=36%P平=28%P客=36%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4196,7 @@
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%P平=29%P客=28%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=45%P平=28%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4612,7 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=32%P平=27%P客=41%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
+          <t>贝叶斯P主=32%P平=26%P客=41%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4768,7 @@
       </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=50%P平=26%P客=24%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4924,7 @@
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=40%P平=30%P客=30%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=40%P平=30%P客=29%|泊松比分1-0|半全场平胜|大小球小2.5(42%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5080,7 @@
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=41%P平=29%P客=30%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+          <t>贝叶斯P主=41%P平=30%P客=30%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5113,6 +5114,31 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
+          <t>方向(双选)</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>信心</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>胆材</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
           <t>比赛日期</t>
         </is>
       </c>
@@ -5140,6 +5166,31 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>P客=41% 优势9%</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
           <t>2026-05-10</t>
         </is>
       </c>
@@ -5167,6 +5218,31 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>P主=37%P平=30%P客=32%</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
           <t>2026-05-10</t>
         </is>
       </c>
@@ -5194,32 +5270,82 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>P主=36%P平=28%P客=36%</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
           <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>英超</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>西汉姆联</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="10" t="inlineStr">
         <is>
           <t>阿森纳</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>P客=45% 优势15%</t>
+        </is>
+      </c>
+      <c r="J118" s="10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
@@ -5248,113 +5374,238 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>P主=37%P平=30%P客=33%</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
           <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>德甲</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>科隆</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="10" t="inlineStr">
         <is>
           <t>海登海姆</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>P主=44% 优势15%</t>
+        </is>
+      </c>
+      <c r="J120" s="10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B121" s="10" t="inlineStr">
         <is>
           <t>德甲</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>美因茨</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D121" s="10" t="inlineStr">
         <is>
           <t>柏林联合</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>P主=44% 优势16%</t>
+        </is>
+      </c>
+      <c r="J121" s="10" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B122" s="10" t="inlineStr">
         <is>
           <t>意甲</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C122" s="10" t="inlineStr">
         <is>
           <t>克雷莫纳</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>比萨</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>P主=46% 优势18%</t>
+        </is>
+      </c>
+      <c r="J122" s="10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B123" s="10" t="inlineStr">
         <is>
           <t>意甲</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>佛罗伦萨</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="10" t="inlineStr">
         <is>
           <t>热那亚</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>P主=45% 优势17%</t>
+        </is>
+      </c>
+      <c r="J123" s="10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
@@ -5383,6 +5634,31 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>P客=41% 优势9%</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
           <t>2026-05-11</t>
         </is>
       </c>
@@ -5410,32 +5686,82 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>P主=41% 优势10%</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
           <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>西甲</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>毕尔巴鄂竞技</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>巴伦西亚</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>P主=48% 优势21%</t>
+        </is>
+      </c>
+      <c r="J126" s="10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
@@ -5464,209 +5790,366 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>P主=39%P平=30%P客=31%</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
           <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>巴塞罗那</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>皇家马德里</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>3.6/10</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>P主=40%P平=27%P客=33%</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>📋 任选9方案（6胆+3双=8注=16元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1. 客胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   4. 客胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   6. 主胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   7. 主胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   8. 主胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   9. 主胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10. 客胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11. 主胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  12. 主胜           (信心4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>方案</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>场次组合</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C144" s="5" t="inlineStr">
         <is>
           <t>每场选择</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>注数</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E144" s="5" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F144" s="5" t="inlineStr">
         <is>
           <t>综合SP</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G144" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>2串1</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>周日016+周日017</t>
         </is>
       </c>
-      <c r="C129" s="9" t="inlineStr">
+      <c r="C145" s="9" t="inlineStr">
         <is>
           <t>·费耶诺德:主胜(1.72)
 ·阿贾克斯:主胜(1.41)</t>
         </is>
       </c>
-      <c r="D129" s="6" t="n">
+      <c r="D145" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E145" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <t>2.43</t>
         </is>
       </c>
-      <c r="G129" s="6" t="inlineStr">
+      <c r="G145" s="6" t="inlineStr">
         <is>
           <t>1.72×1.41=2.43</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>⚠️ 核心信号</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>信号</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>场次</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>解读</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>应对</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="10" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>🟢 高信心(7/10+)</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>015/017/023/024/029</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
         <is>
           <t>5场贝叶斯概率最高，SP均&lt;1.45</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D151" s="6" t="inlineStr">
         <is>
           <t>作胆材/串关核心</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="10" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
         <is>
           <t>🟢 让球SP真实数据</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="B152" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C152" s="6" t="inlineStr">
         <is>
           <t>从500.com让球页提取，非估算</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D152" s="6" t="inlineStr">
         <is>
           <t>可用作让球分析</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="8" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B153" s="6" t="inlineStr">
         <is>
           <t>004/007/011</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C153" s="6" t="inlineStr">
         <is>
           <t>平局概率30-35%，接近主胜</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D153" s="6" t="inlineStr">
         <is>
           <t>双选或慎入</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="8" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="B154" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C154" s="6" t="inlineStr">
         <is>
           <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D154" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="19">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A135:J135"/>
+    <mergeCell ref="A131:J131"/>
+    <mergeCell ref="A140:J140"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A138:J138"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A132:J132"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A137:J137"/>
     <mergeCell ref="A133:J133"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A149:J149"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A136:J136"/>
+    <mergeCell ref="A139:J139"/>
     <mergeCell ref="A113:J113"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
@@ -5688,21 +6171,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>📋 2026-05-10 每场完整分析（30场）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日001 蔚山现代 vs 富川FC [韩职] 13:00</t>
         </is>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1">
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：13:00
 联赛：韩职
@@ -5715,14 +6198,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日002 大阪钢巴 vs 广岛三箭 [日职] 14:00</t>
         </is>
       </c>
     </row>
     <row r="12" ht="130" customHeight="1">
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：14:00
 联赛：日职
@@ -5735,14 +6218,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日003 柏太阳神 vs 川崎前锋 [日职] 15:00</t>
         </is>
       </c>
     </row>
     <row r="20" ht="130" customHeight="1">
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：15:00
 联赛：日职
@@ -5755,14 +6238,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日004 千叶市原 vs 町田泽维 [日职] 16:00</t>
         </is>
       </c>
     </row>
     <row r="28" ht="130" customHeight="1">
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：16:00
 联赛：日职
@@ -5775,14 +6258,14 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日005 维罗纳 vs 科莫 [意甲] 18:30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="130" customHeight="1">
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：意甲
@@ -5795,14 +6278,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日006 杜塞多夫 vs 埃沃斯堡 [德乙] 19:30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="130" customHeight="1">
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：19:30
 联赛：德乙
@@ -5815,14 +6298,14 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日007 马洛卡 vs 比利亚雷 [西甲] 20:00</t>
         </is>
       </c>
     </row>
     <row r="52" ht="130" customHeight="1">
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：20:00
 联赛：西甲
@@ -5835,14 +6318,14 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日008 罗森博格 vs 利勒斯特 [挪超] 20:30</t>
         </is>
       </c>
     </row>
     <row r="60" ht="130" customHeight="1">
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：20:30
 联赛：挪超
@@ -5855,79 +6338,79 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日009 伯恩利 vs 维拉 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="68" ht="130" customHeight="1">
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：5.75 / 4.23 / 1.39
-让球SP(真实)：2.48/3.35/2.34
-差值分析：P主=32% P平=28% P客=40%
+竞彩SP：5.95 / 4.65 / 1.34
+让球SP(真实)：2.65/3.25/2.25
+差值分析：P主=32% P平=27% P客=41%
 推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日010 水晶宫 vs 埃弗顿 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="76" ht="130" customHeight="1">
-      <c r="B76" s="13" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：2.95 / 2.90 / 2.25
-让球SP(真实)：1.50/3.85/4.95
-差值分析：P主=36% P平=30% P客=33%
+竞彩SP：2.72 / 2.80 / 2.48
+让球SP(真实)：1.40/4.22/5.60
+差值分析：P主=37% P平=30% P客=32%
 推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(64%) 备选半全场:平胜
 让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="inlineStr">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日011 诺丁汉 vs 纽卡斯尔 [英超] 21:00</t>
         </is>
       </c>
     </row>
     <row r="84" ht="130" customHeight="1">
-      <c r="B84" s="13" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：英超
-竞彩SP：2.70 / 3.33 / 2.18
-让球SP(真实)：1.51/4.10/4.47
-差值分析：P主=36% P平=28% P客=35%
+竞彩SP：2.88 / 3.35 / 2.07
+让球SP(真实)：1.59/3.88/4.15
+差值分析：P主=36% P平=28% P客=36%
 推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
 让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日012 克雷莫纳 vs 比萨 [意甲] 21:00</t>
         </is>
       </c>
     </row>
     <row r="92" ht="130" customHeight="1">
-      <c r="B92" s="13" t="inlineStr">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：意甲
-竞彩SP：1.60 / 3.45 / 4.65
-让球SP(真实)：3.10/3.25/2.01
+竞彩SP：1.61 / 3.40 / 4.66
+让球SP(真实)：3.20/3.16/2.00
 差值分析：P主=46% P平=28% P客=26%
 推荐：主胜 信心4/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
@@ -5935,38 +6418,38 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="12" t="inlineStr">
+      <c r="A99" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日013 佛罗伦萨 vs 热那亚 [意甲] 21:00</t>
         </is>
       </c>
     </row>
     <row r="100" ht="130" customHeight="1">
-      <c r="B100" s="13" t="inlineStr">
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:00
 联赛：意甲
-竞彩SP：1.85 / 2.95 / 4.00
-让球SP(真实)：4.00/3.30/1.74
-差值分析：P主=44% P平=29% P客=28%
+竞彩SP：1.83 / 2.95 / 4.10
+让球SP(真实)：3.90/3.25/1.77
+差值分析：P主=45% P平=28% P客=27%
 推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
+      <c r="A107" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日014 汉堡 vs 弗赖堡 [德甲] 21:30</t>
         </is>
       </c>
     </row>
     <row r="108" ht="130" customHeight="1">
-      <c r="B108" s="13" t="inlineStr">
+      <c r="B108" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：21:30
 联赛：德甲
-竞彩SP：2.52 / 3.35 / 2.31
+竞彩SP：2.57 / 3.25 / 2.31
 让球SP(真实)：1.47/4.15/4.80
 差值分析：P主=37% P平=30% P客=33%
 推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(57%) 备选半全场:平胜
@@ -5975,14 +6458,14 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="12" t="inlineStr">
+      <c r="A115" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日015 毕尔巴鄂 vs 巴伦西亚 [西甲] 22:15</t>
         </is>
       </c>
     </row>
     <row r="116" ht="130" customHeight="1">
-      <c r="B116" s="13" t="inlineStr">
+      <c r="B116" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:15
 联赛：西甲
@@ -5995,14 +6478,14 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="12" t="inlineStr">
+      <c r="A123" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日016 费耶诺德 vs 阿尔克马 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="124" ht="130" customHeight="1">
-      <c r="B124" s="13" t="inlineStr">
+      <c r="B124" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
@@ -6015,14 +6498,14 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="12" t="inlineStr">
+      <c r="A131" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日017 阿贾克斯 vs 乌德勒支 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="132" ht="130" customHeight="1">
-      <c r="B132" s="13" t="inlineStr">
+      <c r="B132" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
@@ -6035,14 +6518,14 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="12" t="inlineStr">
+      <c r="A139" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日018 格罗宁根 vs 奈梅亨 [荷甲] 22:45</t>
         </is>
       </c>
     </row>
     <row r="140" ht="130" customHeight="1">
-      <c r="B140" s="13" t="inlineStr">
+      <c r="B140" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：22:45
 联赛：荷甲
@@ -6055,14 +6538,14 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="12" t="inlineStr">
+      <c r="A147" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日019 西汉姆联 vs 阿森纳 [英超] 23:30</t>
         </is>
       </c>
     </row>
     <row r="148" ht="130" customHeight="1">
-      <c r="B148" s="13" t="inlineStr">
+      <c r="B148" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：23:30
 联赛：英超
@@ -6075,14 +6558,14 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="12" t="inlineStr">
+      <c r="A155" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日020 科隆 vs 海登海姆 [德甲] 23:30</t>
         </is>
       </c>
     </row>
     <row r="156" ht="130" customHeight="1">
-      <c r="B156" s="13" t="inlineStr">
+      <c r="B156" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：23:30
 联赛：德甲
@@ -6095,34 +6578,34 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="12" t="inlineStr">
+      <c r="A163" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日021 帕尔马 vs 罗马 [意甲] 00:00</t>
         </is>
       </c>
     </row>
     <row r="164" ht="130" customHeight="1">
-      <c r="B164" s="13" t="inlineStr">
+      <c r="B164" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：00:00
 联赛：意甲
-竞彩SP：6.65 / 4.20 / 1.35
-让球SP(真实)：2.61/3.15/2.33
-差值分析：P主=32% P平=27% P客=41%
+竞彩SP：6.90 / 4.30 / 1.33
+让球SP(真实)：2.70/3.08/2.30
+差值分析：P主=32% P平=26% P客=41%
 推荐：客胜 信心4/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:胜负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="12" t="inlineStr">
+      <c r="A171" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日022 奥维耶多 vs 赫塔费 [西甲] 00:30</t>
         </is>
       </c>
     </row>
     <row r="172" ht="130" customHeight="1">
-      <c r="B172" s="13" t="inlineStr">
+      <c r="B172" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：00:30
 联赛：西甲
@@ -6135,14 +6618,14 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="12" t="inlineStr">
+      <c r="A179" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日023 美因茨 vs 柏林联合 [德甲] 01:30</t>
         </is>
       </c>
     </row>
     <row r="180" ht="130" customHeight="1">
-      <c r="B180" s="13" t="inlineStr">
+      <c r="B180" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：01:30
 联赛：德甲
@@ -6155,34 +6638,34 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="12" t="inlineStr">
+      <c r="A187" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日024 吉达联合 vs 达马克 [沙职] 02:00</t>
         </is>
       </c>
     </row>
     <row r="188" ht="130" customHeight="1">
-      <c r="B188" s="13" t="inlineStr">
+      <c r="B188" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙职
-竞彩SP：1.32 / 4.50 / 6.70
-让球SP(真实)：2.08/3.43/2.80
-差值分析：P主=50% P平=26% P客=24%
+竞彩SP：1.35 / 4.50 / 6.00
+让球SP(真实)：2.14/3.43/2.70
+差值分析：P主=49% P平=26% P客=25%
 推荐：主胜 信心1/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="12" t="inlineStr">
+      <c r="A195" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日025 AC米兰 vs 亚特兰大 [意甲] 02:45</t>
         </is>
       </c>
     </row>
     <row r="196" ht="130" customHeight="1">
-      <c r="B196" s="13" t="inlineStr">
+      <c r="B196" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：02:45
 联赛：意甲
@@ -6195,14 +6678,14 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="12" t="inlineStr">
+      <c r="A203" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日026 巴萨 vs 皇马 [西甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="204" ht="130" customHeight="1">
-      <c r="B204" s="13" t="inlineStr">
+      <c r="B204" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：西甲
@@ -6215,34 +6698,34 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="12" t="inlineStr">
+      <c r="A211" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日027 欧塞尔 vs 尼斯 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="212" ht="130" customHeight="1">
-      <c r="B212" s="13" t="inlineStr">
+      <c r="B212" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：法甲
-竞彩SP：2.25 / 3.05 / 2.80
-让球SP(真实)：5.00/3.88/1.49
-差值分析：P主=40% P平=30% P客=30%
+竞彩SP：2.26 / 2.98 / 2.85
+让球SP(真实)：5.10/3.88/1.48
+差值分析：P主=40% P平=30% P客=29%
 推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="12" t="inlineStr">
+      <c r="A219" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日028 巴黎圣曼 vs 布雷斯特 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="220" ht="130" customHeight="1">
-      <c r="B220" s="13" t="inlineStr">
+      <c r="B220" s="14" t="inlineStr">
         <is>
           <t>时间：03:00
 联赛：法甲
@@ -6255,14 +6738,14 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="12" t="inlineStr">
+      <c r="A227" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日029 摩纳哥 vs 里尔 [法甲] 03:00</t>
         </is>
       </c>
     </row>
     <row r="228" ht="130" customHeight="1">
-      <c r="B228" s="13" t="inlineStr">
+      <c r="B228" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：法甲
@@ -6275,20 +6758,20 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="12" t="inlineStr">
+      <c r="A235" s="13" t="inlineStr">
         <is>
           <t>⚽ 周日030 纽约城 vs 哥伦布 [美职] 04:30</t>
         </is>
       </c>
     </row>
     <row r="236" ht="130" customHeight="1">
-      <c r="B236" s="13" t="inlineStr">
+      <c r="B236" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：04:30
 联赛：美职
-竞彩SP：2.25 / 3.35 / 2.59
+竞彩SP：2.25 / 3.25 / 2.65
 让球SP(真实)：4.75/3.97/1.50
-差值分析：P主=41% P平=29% P客=30%
+差值分析：P主=41% P平=30% P客=30%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6352,7 +6835,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>🔗 串关方案（2串1/3串1/4串1/5串1/6串1）</t>
         </is>
@@ -6401,7 +6884,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>A. 胜平负串关</t>
         </is>
@@ -6444,7 +6927,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>B. 比分串关（泊松模型独立计算）</t>
         </is>
@@ -6492,14 +6975,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>C. 混合串关（胜平负+让球穿盘）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>D. 半全场串关（从泊松比分推半全场）</t>
         </is>
